--- a/data-workflow/raw-data/mim_variables.xlsx
+++ b/data-workflow/raw-data/mim_variables.xlsx
@@ -8,9 +8,8 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\este.de.ahora\Documents\_investigacion\00_Doctorado\00_Tesis-PhD\PhD\data-workflow\raw-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9A62EE8-6343-4C3E-AB43-103F2E9E2207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D9E3996-4EE8-4128-828D-DECA4184931D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" xr2:uid="{1C7603B9-061D-4530-A6F0-43647F49C73A}"/>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" activeTab="1" xr2:uid="{DF7805F5-E45D-47F7-961F-4760F5F8126C}"/>
   </bookViews>
   <sheets>
@@ -31,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="313">
   <si>
     <t>Nivel</t>
   </si>
@@ -111,9 +110,6 @@
     <t>in_SUP_t_lab</t>
   </si>
   <si>
-    <t>in_timeTRA</t>
-  </si>
-  <si>
     <t>in_timeREP</t>
   </si>
   <si>
@@ -138,9 +134,6 @@
     <t>v_MOT</t>
   </si>
   <si>
-    <t>v_TACT</t>
-  </si>
-  <si>
     <t>v_TVIA</t>
   </si>
   <si>
@@ -246,60 +239,6 @@
     <t>inT_Q5</t>
   </si>
   <si>
-    <t>inTrab_Q1</t>
-  </si>
-  <si>
-    <t>inTrab_Q2</t>
-  </si>
-  <si>
-    <t>inTrab_Q3</t>
-  </si>
-  <si>
-    <t>inTrab_Q4</t>
-  </si>
-  <si>
-    <t>inTrab_Q5</t>
-  </si>
-  <si>
-    <t>inTrab_NO</t>
-  </si>
-  <si>
-    <t>inRepr_Q1</t>
-  </si>
-  <si>
-    <t>inRepr_Q2</t>
-  </si>
-  <si>
-    <t>inRepr_Q3</t>
-  </si>
-  <si>
-    <t>inRepr_Q4</t>
-  </si>
-  <si>
-    <t>inRepr_Q5</t>
-  </si>
-  <si>
-    <t>inRepr_NO</t>
-  </si>
-  <si>
-    <t>inRecr_Q1</t>
-  </si>
-  <si>
-    <t>inRecr_Q2</t>
-  </si>
-  <si>
-    <t>inRecr_Q3</t>
-  </si>
-  <si>
-    <t>inRecr_Q4</t>
-  </si>
-  <si>
-    <t>inRecr_Q5</t>
-  </si>
-  <si>
-    <t>inRecr_NO</t>
-  </si>
-  <si>
     <t>inEst_Q1</t>
   </si>
   <si>
@@ -492,9 +431,6 @@
     <t>v_TVIA_lab</t>
   </si>
   <si>
-    <t>v_TACT_lab</t>
-  </si>
-  <si>
     <t>var_lab</t>
   </si>
   <si>
@@ -973,6 +909,66 @@
   </si>
   <si>
     <t>inPolicentr_Q5</t>
+  </si>
+  <si>
+    <t>in_TACT</t>
+  </si>
+  <si>
+    <t>in_timeLAB</t>
+  </si>
+  <si>
+    <t>inLab_NO</t>
+  </si>
+  <si>
+    <t>inLab_Q1</t>
+  </si>
+  <si>
+    <t>inLab_Q2</t>
+  </si>
+  <si>
+    <t>inLab_Q3</t>
+  </si>
+  <si>
+    <t>inLab_Q4</t>
+  </si>
+  <si>
+    <t>inLab_Q5</t>
+  </si>
+  <si>
+    <t>inRep_NO</t>
+  </si>
+  <si>
+    <t>inRep_Q1</t>
+  </si>
+  <si>
+    <t>inRep_Q2</t>
+  </si>
+  <si>
+    <t>inRep_Q3</t>
+  </si>
+  <si>
+    <t>inRep_Q4</t>
+  </si>
+  <si>
+    <t>inRep_Q5</t>
+  </si>
+  <si>
+    <t>inRec_NO</t>
+  </si>
+  <si>
+    <t>inRec_Q1</t>
+  </si>
+  <si>
+    <t>inRec_Q2</t>
+  </si>
+  <si>
+    <t>inRec_Q3</t>
+  </si>
+  <si>
+    <t>inRec_Q4</t>
+  </si>
+  <si>
+    <t>inRec_Q5</t>
   </si>
 </sst>
 </file>
@@ -1579,16 +1575,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.95" x14ac:dyDescent="0.25">
@@ -1596,7 +1592,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C2" s="38" t="s">
         <v>2</v>
@@ -1612,7 +1608,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C3" s="37" t="s">
         <v>3</v>
@@ -1628,7 +1624,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="C4" s="37" t="s">
         <v>4</v>
@@ -1642,7 +1638,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="C5" s="39" t="s">
         <v>5</v>
@@ -1655,10 +1651,10 @@
     </row>
     <row r="6" spans="1:6" ht="14.95" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C6" s="38" t="s">
         <v>6</v>
@@ -1667,18 +1663,18 @@
         <v>9</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="14.95" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C7" s="37" t="s">
         <v>7</v>
@@ -1687,18 +1683,18 @@
         <v>4</v>
       </c>
       <c r="E7" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="14.95" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C8" s="37" t="s">
         <v>8</v>
@@ -1707,18 +1703,18 @@
         <v>2</v>
       </c>
       <c r="E8" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C9" s="37" t="s">
         <v>9</v>
@@ -1727,138 +1723,138 @@
         <v>3</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
       <c r="D10" s="11">
         <v>5</v>
       </c>
       <c r="E10" s="42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="D11" s="11">
         <v>5</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="D12" s="11">
         <v>5</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="42.8" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
       <c r="D13" s="11">
         <v>5</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="C14" s="40" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="D14" s="11">
         <v>5</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="14.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="C15" s="40" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="D15" s="11">
         <v>5</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="14.95" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="C16" s="37" t="s">
         <v>10</v>
@@ -1867,18 +1863,18 @@
         <v>3</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="14.95" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="C17" s="37" t="s">
         <v>11</v>
@@ -1887,402 +1883,404 @@
         <v>3</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="D18" s="15"/>
       <c r="E18" s="15" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C19" s="36" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="15" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C20" s="36" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
       <c r="D20" s="15"/>
       <c r="E20" s="15" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="42.8" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C21" s="41" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="D21" s="18"/>
       <c r="E21" s="18" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="14.95" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D22" s="11">
         <v>4</v>
       </c>
       <c r="E22" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="14.95" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="C23" s="37" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="D23" s="11">
         <v>5</v>
       </c>
       <c r="E23" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F23" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="C24" s="40" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
       <c r="D24" s="11">
         <v>5</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="C25" s="40" t="s">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="D25" s="11">
         <v>5</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D26" s="15"/>
       <c r="E26" s="15" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="C27" s="37" t="s">
-        <v>36</v>
+        <v>190</v>
+      </c>
+      <c r="C27" s="40" t="s">
+        <v>191</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="15" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="28.55" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="C28" s="40" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="D28" s="15"/>
       <c r="E28" s="15" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>51</v>
+        <v>181</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="10">
+        <v>9</v>
+      </c>
+      <c r="E29" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="C29" s="40" t="s">
-        <v>215</v>
-      </c>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>202</v>
+      <c r="F29" s="3" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C30" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" s="10">
-        <v>9</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>149</v>
+      <c r="A30" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C30" s="40" t="s">
+        <v>197</v>
+      </c>
+      <c r="D30" s="11">
+        <v>4</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="C31" s="40" t="s">
-        <v>218</v>
+        <v>113</v>
+      </c>
+      <c r="C31" s="52" t="s">
+        <v>272</v>
       </c>
       <c r="D31" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E31" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F31" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F31" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:6" ht="30.1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="C32" s="52" t="s">
-        <v>153</v>
+        <v>115</v>
+      </c>
+      <c r="C32" s="37" t="s">
+        <v>21</v>
       </c>
       <c r="D32" s="11">
         <v>5</v>
       </c>
       <c r="E32" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F32" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="30.1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="C33" s="37" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D33" s="11">
         <v>5</v>
       </c>
       <c r="E33" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F33" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F33" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="30.1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:6" ht="59.95" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="C34" s="37" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D34" s="11">
         <v>5</v>
       </c>
       <c r="E34" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F34" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="59.95" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="C35" s="37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D35" s="11">
         <v>5</v>
       </c>
       <c r="E35" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F35" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F35" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="59.95" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:6" ht="42.8" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="C36" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="D36" s="11">
-        <v>5</v>
+        <v>25</v>
+      </c>
+      <c r="D36" s="47">
+        <v>4</v>
       </c>
       <c r="E36" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F36" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F36" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="42.8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="C37" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="D37" s="47">
-        <v>4</v>
+        <v>294</v>
+      </c>
+      <c r="D37" s="11">
+        <v>6</v>
       </c>
       <c r="E37" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F37" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F37" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:6" ht="42.8" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="C38" s="37" t="s">
         <v>26</v>
@@ -2291,18 +2289,18 @@
         <v>6</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="42.8" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="C39" s="37" t="s">
         <v>27</v>
@@ -2311,18 +2309,18 @@
         <v>6</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="C40" s="37" t="s">
         <v>28</v>
@@ -2331,118 +2329,118 @@
         <v>6</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>145</v>
+        <v>37</v>
+      </c>
+      <c r="B41" s="43" t="s">
+        <v>127</v>
       </c>
       <c r="C41" s="37" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D41" s="11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B42" s="43" t="s">
-        <v>147</v>
-      </c>
-      <c r="C42" s="37" t="s">
-        <v>33</v>
+        <v>189</v>
+      </c>
+      <c r="C42" s="40" t="s">
+        <v>186</v>
       </c>
       <c r="D42" s="11">
         <v>5</v>
       </c>
       <c r="E42" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F42" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="F42" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="28.55" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B43" s="43" t="s">
-        <v>210</v>
+        <v>37</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>182</v>
       </c>
       <c r="C43" s="40" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="D43" s="11">
         <v>5</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="14.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="C44" s="40" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="D44" s="11">
         <v>5</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="14.3" customHeight="1" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="C45" s="40" t="s">
-        <v>208</v>
+        <v>117</v>
+      </c>
+      <c r="C45" s="37" t="s">
+        <v>29</v>
       </c>
       <c r="D45" s="11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="14.95" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="C46" s="37" t="s">
         <v>30</v>
@@ -2451,161 +2449,157 @@
         <v>3</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="14.95" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>138</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>196</v>
       </c>
       <c r="C47" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="D47" s="11">
-        <v>3</v>
-      </c>
-      <c r="E47" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>52</v>
+        <v>198</v>
+      </c>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="F47" s="13" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>217</v>
+        <v>113</v>
       </c>
       <c r="C48" s="37" t="s">
-        <v>219</v>
-      </c>
-      <c r="D48" s="15">
-        <v>5</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="D48" s="15"/>
       <c r="E48" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="F48" s="13" t="s">
         <v>42</v>
-      </c>
-      <c r="F48" s="13" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="C49" s="37" t="s">
         <v>16</v>
       </c>
       <c r="D49" s="15"/>
       <c r="E49" s="15" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="F49" s="13"/>
     </row>
     <row r="50" spans="1:6" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="C50" s="37" t="s">
         <v>17</v>
       </c>
       <c r="D50" s="15"/>
       <c r="E50" s="15" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="F50" s="13"/>
     </row>
     <row r="51" spans="1:6" ht="42.8" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="C51" s="37" t="s">
         <v>18</v>
       </c>
       <c r="D51" s="15"/>
       <c r="E51" s="15" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="F51" s="13"/>
     </row>
     <row r="52" spans="1:6" ht="42.8" x14ac:dyDescent="0.25">
       <c r="A52" s="13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C52" s="37" t="s">
         <v>19</v>
       </c>
       <c r="D52" s="15"/>
       <c r="E52" s="15" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="F52" s="13"/>
     </row>
     <row r="53" spans="1:6" ht="42.8" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="C53" s="37" t="s">
         <v>20</v>
       </c>
       <c r="D53" s="15"/>
       <c r="E53" s="15" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="F53" s="13"/>
     </row>
     <row r="54" spans="1:6" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A54" s="13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="C54" s="37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D54" s="15"/>
       <c r="E54" s="15" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="F54" s="13"/>
     </row>
     <row r="55" spans="1:6" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A55" s="16" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B55" s="17" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="C55" s="41" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="D55" s="18"/>
       <c r="E55" s="18" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="F55" s="16"/>
     </row>
@@ -2633,42 +2627,42 @@
         <v>0</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="E1" s="26" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="F1" s="26" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="G1" s="26" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="H1" s="26" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="14.95" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B2" s="25" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="F2" s="32">
         <v>1</v>
@@ -2682,19 +2676,19 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B3" s="25" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D3" s="25" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="F3" s="32">
         <v>1</v>
@@ -2708,19 +2702,19 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B4" s="25" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="F4" s="32">
         <v>1</v>
@@ -2734,19 +2728,19 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B5" s="25" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="F5" s="32">
         <v>1</v>
@@ -2760,19 +2754,19 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B6" s="25" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="F6" s="32">
         <v>1</v>
@@ -2786,19 +2780,19 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B7" s="25" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="F7" s="32">
         <v>1</v>
@@ -2812,19 +2806,19 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B8" s="25" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="F8" s="32">
         <v>1</v>
@@ -2838,19 +2832,19 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B9" s="25" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="F9" s="32">
         <v>1</v>
@@ -2864,19 +2858,19 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B10" s="22" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="F10" s="29">
         <v>1</v>
@@ -2890,19 +2884,19 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B11" s="25" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="F11" s="32">
         <v>0</v>
@@ -2916,19 +2910,19 @@
     </row>
     <row r="12" spans="1:8" ht="14.95" x14ac:dyDescent="0.25">
       <c r="A12" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B12" s="25" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="F12" s="32">
         <v>0</v>
@@ -2942,19 +2936,19 @@
     </row>
     <row r="13" spans="1:8" ht="14.95" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B13" s="21" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="F13" s="28">
         <v>0</v>
@@ -2968,19 +2962,19 @@
     </row>
     <row r="14" spans="1:8" ht="14.95" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B14" s="22" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="E14" s="29" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="F14" s="29">
         <v>0</v>
@@ -2994,19 +2988,19 @@
     </row>
     <row r="15" spans="1:8" ht="14.95" x14ac:dyDescent="0.25">
       <c r="A15" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B15" s="25" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="F15" s="32">
         <v>0</v>
@@ -3020,19 +3014,19 @@
     </row>
     <row r="16" spans="1:8" ht="14.95" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="F16" s="29">
         <v>0</v>
@@ -3046,19 +3040,19 @@
     </row>
     <row r="17" spans="1:8" ht="14.95" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="E17" s="32" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="F17" s="32">
         <v>0</v>
@@ -3072,19 +3066,19 @@
     </row>
     <row r="18" spans="1:8" ht="14.95" x14ac:dyDescent="0.25">
       <c r="A18" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B18" s="25" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="F18" s="32">
         <v>0</v>
@@ -3098,19 +3092,19 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B19" s="22" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="E19" s="29" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="F19" s="29">
         <v>0</v>
@@ -3124,19 +3118,19 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
       <c r="C20" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="E20" s="32" t="s">
         <v>172</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>223</v>
-      </c>
-      <c r="E20" s="32" t="s">
-        <v>193</v>
       </c>
       <c r="F20" s="32">
         <v>0</v>
@@ -3150,19 +3144,19 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
       <c r="C21" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="E21" s="32" t="s">
         <v>172</v>
-      </c>
-      <c r="D21" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="E21" s="32" t="s">
-        <v>193</v>
       </c>
       <c r="F21" s="32">
         <v>0</v>
@@ -3176,19 +3170,19 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
       <c r="C22" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>204</v>
+      </c>
+      <c r="E22" s="32" t="s">
         <v>172</v>
-      </c>
-      <c r="D22" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="E22" s="32" t="s">
-        <v>193</v>
       </c>
       <c r="F22" s="32">
         <v>0</v>
@@ -3202,19 +3196,19 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="21" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
       <c r="C23" s="21" t="s">
+        <v>151</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="E23" s="28" t="s">
         <v>172</v>
-      </c>
-      <c r="D23" s="21" t="s">
-        <v>226</v>
-      </c>
-      <c r="E23" s="28" t="s">
-        <v>193</v>
       </c>
       <c r="F23" s="28">
         <v>0</v>
@@ -3228,19 +3222,19 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
       <c r="C24" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>206</v>
+      </c>
+      <c r="E24" s="29" t="s">
         <v>172</v>
-      </c>
-      <c r="D24" s="22" t="s">
-        <v>227</v>
-      </c>
-      <c r="E24" s="29" t="s">
-        <v>193</v>
       </c>
       <c r="F24" s="29">
         <v>0</v>
@@ -3254,19 +3248,19 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B25" s="25" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="D25" s="25" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
       <c r="E25" s="32" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="F25" s="32">
         <v>1</v>
@@ -3280,19 +3274,19 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B26" s="25" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="D26" s="25" t="s">
-        <v>229</v>
+        <v>208</v>
       </c>
       <c r="E26" s="32" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="F26" s="32">
         <v>1</v>
@@ -3306,19 +3300,19 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B27" s="25" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="D27" s="25" t="s">
-        <v>230</v>
+        <v>209</v>
       </c>
       <c r="E27" s="32" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="F27" s="32">
         <v>1</v>
@@ -3332,19 +3326,19 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B28" s="25" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="25" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="E28" s="32" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="F28" s="32">
         <v>1</v>
@@ -3358,19 +3352,19 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B29" s="22" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="D29" s="22" t="s">
-        <v>232</v>
+        <v>211</v>
       </c>
       <c r="E29" s="29" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="F29" s="29">
         <v>1</v>
@@ -3384,19 +3378,19 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B30" s="25" t="s">
         <v>13</v>
       </c>
       <c r="C30" s="25" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="D30" s="25" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="E30" s="32" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="F30" s="32">
         <v>1</v>
@@ -3410,19 +3404,19 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B31" s="25" t="s">
         <v>13</v>
       </c>
       <c r="C31" s="25" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="D31" s="25" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="E31" s="32" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="F31" s="32">
         <v>1</v>
@@ -3436,19 +3430,19 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B32" s="25" t="s">
         <v>13</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="D32" s="25" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
       <c r="E32" s="32" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="F32" s="32">
         <v>1</v>
@@ -3462,19 +3456,19 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B33" s="25" t="s">
         <v>13</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="D33" s="25" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
       <c r="E33" s="32" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="F33" s="32">
         <v>1</v>
@@ -3488,19 +3482,19 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="22" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B34" s="22" t="s">
         <v>13</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="D34" s="22" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="E34" s="29" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="F34" s="29">
         <v>1</v>
@@ -3514,19 +3508,19 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B35" s="25" t="s">
         <v>14</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="E35" s="32" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="F35" s="32">
         <v>1</v>
@@ -3540,19 +3534,19 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B36" s="25" t="s">
         <v>14</v>
       </c>
       <c r="C36" s="25" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="D36" s="25" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
       <c r="E36" s="32" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="F36" s="32">
         <v>1</v>
@@ -3566,19 +3560,19 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B37" s="25" t="s">
         <v>14</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="D37" s="25" t="s">
-        <v>240</v>
+        <v>219</v>
       </c>
       <c r="E37" s="32" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="F37" s="32">
         <v>1</v>
@@ -3592,19 +3586,19 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="21" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B38" s="21" t="s">
         <v>14</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="E38" s="28" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="F38" s="28">
         <v>1</v>
@@ -3618,19 +3612,19 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="22" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B39" s="22" t="s">
         <v>14</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="D39" s="22" t="s">
-        <v>242</v>
+        <v>221</v>
       </c>
       <c r="E39" s="29" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="F39" s="29">
         <v>1</v>
@@ -3644,19 +3638,19 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B40" s="25" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="D40" s="25" t="s">
-        <v>249</v>
+        <v>228</v>
       </c>
       <c r="E40" s="32" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="F40" s="44">
         <v>0</v>
@@ -3670,19 +3664,19 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="21" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B41" s="21" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="D41" s="21" t="s">
-        <v>250</v>
+        <v>229</v>
       </c>
       <c r="E41" s="28" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="F41" s="45">
         <v>0</v>
@@ -3696,19 +3690,19 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="21" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B42" s="21" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="D42" s="21" t="s">
-        <v>251</v>
+        <v>230</v>
       </c>
       <c r="E42" s="28" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="F42" s="45">
         <v>0</v>
@@ -3722,19 +3716,19 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="21" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B43" s="21" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="D43" s="21" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="E43" s="28" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="F43" s="45">
         <v>0</v>
@@ -3748,19 +3742,19 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="22" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B44" s="22" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="C44" s="22" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="D44" s="22" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="E44" s="29" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="F44" s="46">
         <v>0</v>
@@ -3774,19 +3768,19 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B45" s="25" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="C45" s="25" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="D45" s="25" t="s">
-        <v>254</v>
+        <v>233</v>
       </c>
       <c r="E45" s="32" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="F45" s="44">
         <v>0</v>
@@ -3800,19 +3794,19 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="21" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="D46" s="21" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="E46" s="28" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="F46" s="45">
         <v>0</v>
@@ -3826,19 +3820,19 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="21" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="C47" s="21" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="D47" s="21" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="E47" s="28" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="F47" s="45">
         <v>0</v>
@@ -3852,19 +3846,19 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="21" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="D48" s="21" t="s">
-        <v>257</v>
+        <v>236</v>
       </c>
       <c r="E48" s="28" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="F48" s="45">
         <v>0</v>
@@ -3878,19 +3872,19 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="22" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B49" s="22" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="D49" s="22" t="s">
-        <v>258</v>
+        <v>237</v>
       </c>
       <c r="E49" s="29" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="F49" s="46">
         <v>0</v>
@@ -3904,19 +3898,19 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B50" s="25" t="s">
         <v>10</v>
       </c>
       <c r="C50" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="D50" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="E50" s="28" t="s">
         <v>161</v>
-      </c>
-      <c r="D50" s="25" t="s">
-        <v>243</v>
-      </c>
-      <c r="E50" s="28" t="s">
-        <v>182</v>
       </c>
       <c r="F50" s="32">
         <v>0</v>
@@ -3930,19 +3924,19 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="21" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B51" s="21" t="s">
         <v>10</v>
       </c>
       <c r="C51" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="D51" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="E51" s="28" t="s">
         <v>161</v>
-      </c>
-      <c r="D51" s="21" t="s">
-        <v>244</v>
-      </c>
-      <c r="E51" s="28" t="s">
-        <v>182</v>
       </c>
       <c r="F51" s="28">
         <v>0</v>
@@ -3956,19 +3950,19 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="22" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B52" s="22" t="s">
         <v>10</v>
       </c>
       <c r="C52" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="D52" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="E52" s="29" t="s">
         <v>161</v>
-      </c>
-      <c r="D52" s="22" t="s">
-        <v>245</v>
-      </c>
-      <c r="E52" s="29" t="s">
-        <v>182</v>
       </c>
       <c r="F52" s="29">
         <v>0</v>
@@ -3982,19 +3976,19 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B53" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C53" s="25" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="D53" s="25" t="s">
-        <v>246</v>
+        <v>225</v>
       </c>
       <c r="E53" s="28" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="F53" s="32">
         <v>0</v>
@@ -4008,19 +4002,19 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="25" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B54" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C54" s="25" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="D54" s="25" t="s">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="E54" s="28" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="F54" s="32">
         <v>0</v>
@@ -4034,19 +4028,19 @@
     </row>
     <row r="55" spans="1:9" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="22" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B55" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C55" s="22" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="D55" s="22" t="s">
-        <v>248</v>
+        <v>227</v>
       </c>
       <c r="E55" s="29" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="F55" s="29">
         <v>0</v>
@@ -4060,19 +4054,19 @@
     </row>
     <row r="56" spans="1:9" ht="14.95" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A56" s="20" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B56" s="20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="D56" s="33" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="E56" s="34" t="s">
-        <v>189</v>
+        <v>168</v>
       </c>
       <c r="F56" s="34">
         <v>1</v>
@@ -4086,19 +4080,19 @@
     </row>
     <row r="57" spans="1:9" ht="14.95" x14ac:dyDescent="0.25">
       <c r="A57" s="21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B57" s="21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C57" s="21" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="D57" s="21" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="E57" s="28" t="s">
-        <v>189</v>
+        <v>168</v>
       </c>
       <c r="F57" s="28">
         <v>1</v>
@@ -4112,19 +4106,19 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B58" s="21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="E58" s="28" t="s">
-        <v>189</v>
+        <v>168</v>
       </c>
       <c r="F58" s="28">
         <v>1</v>
@@ -4138,19 +4132,19 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="22" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B59" s="22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C59" s="22" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="D59" s="22" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="E59" s="29" t="s">
-        <v>189</v>
+        <v>168</v>
       </c>
       <c r="F59" s="29">
         <v>1</v>
@@ -4164,19 +4158,19 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B60" s="21" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="D60" s="21" t="s">
-        <v>288</v>
+        <v>267</v>
       </c>
       <c r="E60" s="28" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="F60" s="28">
         <v>1</v>
@@ -4190,19 +4184,19 @@
     </row>
     <row r="61" spans="1:9" ht="14.95" x14ac:dyDescent="0.25">
       <c r="A61" s="21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B61" s="21" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="C61" s="21" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="D61" s="21" t="s">
-        <v>289</v>
+        <v>268</v>
       </c>
       <c r="E61" s="28" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="F61" s="28">
         <v>1</v>
@@ -4216,19 +4210,19 @@
     </row>
     <row r="62" spans="1:9" ht="14.95" x14ac:dyDescent="0.25">
       <c r="A62" s="21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B62" s="21" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="C62" s="21" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="D62" s="21" t="s">
-        <v>290</v>
+        <v>269</v>
       </c>
       <c r="E62" s="28" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="F62" s="28">
         <v>1</v>
@@ -4242,19 +4236,19 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B63" s="21" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="C63" s="21" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="D63" s="21" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="E63" s="28" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="F63" s="28">
         <v>1</v>
@@ -4268,19 +4262,19 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="22" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B64" s="22" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="C64" s="22" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="D64" s="22" t="s">
-        <v>292</v>
+        <v>271</v>
       </c>
       <c r="E64" s="29" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="F64" s="29">
         <v>1</v>
@@ -4295,19 +4289,19 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B65" s="21" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
       <c r="C65" s="21" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="D65" s="49" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
       <c r="E65" s="28" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="F65" s="45">
         <v>0</v>
@@ -4321,19 +4315,19 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B66" s="21" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
       <c r="C66" s="21" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="D66" s="21" t="s">
-        <v>279</v>
+        <v>258</v>
       </c>
       <c r="E66" s="28" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="F66" s="45">
         <v>0</v>
@@ -4347,19 +4341,19 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B67" s="21" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
       <c r="C67" s="21" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="D67" s="21" t="s">
-        <v>280</v>
+        <v>259</v>
       </c>
       <c r="E67" s="28" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="F67" s="45">
         <v>0</v>
@@ -4373,19 +4367,19 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B68" s="21" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
       <c r="C68" s="21" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="D68" s="21" t="s">
-        <v>281</v>
+        <v>260</v>
       </c>
       <c r="E68" s="28" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="F68" s="45">
         <v>0</v>
@@ -4399,19 +4393,19 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="22" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B69" s="22" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
       <c r="C69" s="22" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="D69" s="50" t="s">
-        <v>282</v>
+        <v>261</v>
       </c>
       <c r="E69" s="29" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="F69" s="46">
         <v>0</v>
@@ -4426,19 +4420,19 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B70" s="21" t="s">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="C70" s="21" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="D70" s="49" t="s">
-        <v>283</v>
+        <v>262</v>
       </c>
       <c r="E70" s="28" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="F70" s="45">
         <v>0</v>
@@ -4452,19 +4446,19 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B71" s="21" t="s">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="C71" s="21" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="D71" s="21" t="s">
-        <v>284</v>
+        <v>263</v>
       </c>
       <c r="E71" s="28" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="F71" s="45">
         <v>0</v>
@@ -4478,19 +4472,19 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B72" s="21" t="s">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="C72" s="21" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="D72" s="21" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="E72" s="28" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="F72" s="45">
         <v>0</v>
@@ -4504,19 +4498,19 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B73" s="21" t="s">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="C73" s="21" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="D73" s="21" t="s">
-        <v>286</v>
+        <v>265</v>
       </c>
       <c r="E73" s="28" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="F73" s="45">
         <v>0</v>
@@ -4530,19 +4524,19 @@
     </row>
     <row r="74" spans="1:9" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="24" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B74" s="24" t="s">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="C74" s="24" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="D74" s="51" t="s">
-        <v>287</v>
+        <v>266</v>
       </c>
       <c r="E74" s="31" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="F74" s="48">
         <v>0</v>
@@ -4556,19 +4550,19 @@
     </row>
     <row r="75" spans="1:9" ht="14.95" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A75" s="20" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B75" s="20" t="s">
         <v>15</v>
       </c>
       <c r="C75" s="20" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="D75" s="20" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E75" s="27" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="F75" s="27">
         <v>1</v>
@@ -4582,19 +4576,19 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B76" s="21" t="s">
         <v>15</v>
       </c>
       <c r="C76" s="21" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="D76" s="21" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E76" s="28" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="F76" s="28">
         <v>1</v>
@@ -4608,19 +4602,19 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B77" s="21" t="s">
         <v>15</v>
       </c>
       <c r="C77" s="21" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="D77" s="21" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E77" s="28" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="F77" s="28">
         <v>1</v>
@@ -4634,19 +4628,19 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B78" s="21" t="s">
         <v>15</v>
       </c>
       <c r="C78" s="21" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="D78" s="21" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E78" s="28" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="F78" s="28">
         <v>1</v>
@@ -4660,19 +4654,19 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B79" s="21" t="s">
         <v>15</v>
       </c>
       <c r="C79" s="21" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="D79" s="21" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E79" s="28" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="F79" s="28">
         <v>1</v>
@@ -4686,19 +4680,19 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B80" s="21" t="s">
         <v>15</v>
       </c>
       <c r="C80" s="21" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="D80" s="21" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E80" s="28" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="F80" s="28">
         <v>1</v>
@@ -4712,19 +4706,19 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B81" s="21" t="s">
         <v>15</v>
       </c>
       <c r="C81" s="21" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="D81" s="21" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E81" s="28" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="F81" s="28">
         <v>1</v>
@@ -4738,19 +4732,19 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B82" s="21" t="s">
         <v>15</v>
       </c>
       <c r="C82" s="21" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="D82" s="21" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E82" s="28" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="F82" s="28">
         <v>1</v>
@@ -4764,19 +4758,19 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B83" s="22" t="s">
         <v>15</v>
       </c>
       <c r="C83" s="22" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="D83" s="22" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E83" s="29" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="F83" s="29">
         <v>1</v>
@@ -4790,19 +4784,19 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="23" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B84" s="23" t="s">
-        <v>293</v>
+        <v>272</v>
       </c>
       <c r="C84" s="23" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="D84" s="23" t="s">
-        <v>294</v>
+        <v>273</v>
       </c>
       <c r="E84" s="28" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="F84" s="53">
         <v>0</v>
@@ -4816,19 +4810,19 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B85" s="21" t="s">
-        <v>293</v>
+        <v>272</v>
       </c>
       <c r="C85" s="21" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="D85" s="21" t="s">
-        <v>295</v>
+        <v>274</v>
       </c>
       <c r="E85" s="28" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="F85" s="45">
         <v>0</v>
@@ -4842,19 +4836,19 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B86" s="21" t="s">
-        <v>293</v>
+        <v>272</v>
       </c>
       <c r="C86" s="21" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="D86" s="21" t="s">
-        <v>296</v>
+        <v>275</v>
       </c>
       <c r="E86" s="28" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="F86" s="45">
         <v>0</v>
@@ -4868,19 +4862,19 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B87" s="21" t="s">
-        <v>293</v>
+        <v>272</v>
       </c>
       <c r="C87" s="21" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="D87" s="21" t="s">
-        <v>297</v>
+        <v>276</v>
       </c>
       <c r="E87" s="28" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="F87" s="45">
         <v>0</v>
@@ -4894,19 +4888,19 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B88" s="22" t="s">
-        <v>293</v>
+        <v>272</v>
       </c>
       <c r="C88" s="22" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="D88" s="22" t="s">
-        <v>298</v>
+        <v>277</v>
       </c>
       <c r="E88" s="29" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="F88" s="46">
         <v>0</v>
@@ -4920,19 +4914,19 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B89" s="21" t="s">
         <v>21</v>
       </c>
       <c r="C89" s="21" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="D89" s="21" t="s">
-        <v>259</v>
+        <v>238</v>
       </c>
       <c r="E89" s="28" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="F89" s="28">
         <v>1</v>
@@ -4946,19 +4940,19 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B90" s="21" t="s">
         <v>21</v>
       </c>
       <c r="C90" s="21" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="D90" s="21" t="s">
-        <v>260</v>
+        <v>239</v>
       </c>
       <c r="E90" s="28" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="F90" s="28">
         <v>1</v>
@@ -4972,19 +4966,19 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B91" s="21" t="s">
         <v>21</v>
       </c>
       <c r="C91" s="21" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="D91" s="21" t="s">
-        <v>261</v>
+        <v>240</v>
       </c>
       <c r="E91" s="28" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="F91" s="28">
         <v>1</v>
@@ -4998,19 +4992,19 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B92" s="21" t="s">
         <v>21</v>
       </c>
       <c r="C92" s="21" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="D92" s="21" t="s">
-        <v>262</v>
+        <v>241</v>
       </c>
       <c r="E92" s="28" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="F92" s="28">
         <v>1</v>
@@ -5024,19 +5018,19 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B93" s="22" t="s">
         <v>21</v>
       </c>
       <c r="C93" s="22" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="D93" s="22" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="E93" s="29" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="F93" s="29">
         <v>1</v>
@@ -5050,19 +5044,19 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B94" s="21" t="s">
         <v>22</v>
       </c>
       <c r="C94" s="21" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="D94" s="21" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E94" s="28" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="F94" s="28">
         <v>1</v>
@@ -5076,19 +5070,19 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B95" s="21" t="s">
         <v>22</v>
       </c>
       <c r="C95" s="21" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="D95" s="21" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E95" s="28" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="F95" s="28">
         <v>1</v>
@@ -5102,19 +5096,19 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B96" s="21" t="s">
         <v>22</v>
       </c>
       <c r="C96" s="21" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="D96" s="21" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E96" s="28" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="F96" s="28">
         <v>1</v>
@@ -5128,19 +5122,19 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B97" s="21" t="s">
         <v>22</v>
       </c>
       <c r="C97" s="21" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="D97" s="21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E97" s="28" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="F97" s="28">
         <v>1</v>
@@ -5154,19 +5148,19 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B98" s="22" t="s">
         <v>22</v>
       </c>
       <c r="C98" s="22" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="D98" s="22" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E98" s="29" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
       <c r="F98" s="29">
         <v>1</v>
@@ -5180,19 +5174,19 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B99" s="21" t="s">
         <v>23</v>
       </c>
       <c r="C99" s="21" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="D99" s="21" t="s">
-        <v>264</v>
+        <v>243</v>
       </c>
       <c r="E99" s="28" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="F99" s="28">
         <v>1</v>
@@ -5206,19 +5200,19 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B100" s="21" t="s">
         <v>23</v>
       </c>
       <c r="C100" s="21" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="D100" s="21" t="s">
-        <v>265</v>
+        <v>244</v>
       </c>
       <c r="E100" s="28" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="F100" s="28">
         <v>1</v>
@@ -5232,19 +5226,19 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B101" s="21" t="s">
         <v>23</v>
       </c>
       <c r="C101" s="21" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="D101" s="21" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="E101" s="28" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="F101" s="28">
         <v>1</v>
@@ -5258,19 +5252,19 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B102" s="21" t="s">
         <v>23</v>
       </c>
       <c r="C102" s="21" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="D102" s="21" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="E102" s="28" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="F102" s="28">
         <v>1</v>
@@ -5284,19 +5278,19 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B103" s="22" t="s">
         <v>23</v>
       </c>
       <c r="C103" s="22" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="D103" s="22" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
       <c r="E103" s="29" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="F103" s="29">
         <v>1</v>
@@ -5310,19 +5304,19 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B104" s="21" t="s">
         <v>24</v>
       </c>
       <c r="C104" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="D104" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="E104" s="28" t="s">
         <v>167</v>
-      </c>
-      <c r="D104" s="21" t="s">
-        <v>269</v>
-      </c>
-      <c r="E104" s="28" t="s">
-        <v>188</v>
       </c>
       <c r="F104" s="28">
         <v>1</v>
@@ -5336,19 +5330,19 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B105" s="21" t="s">
         <v>24</v>
       </c>
       <c r="C105" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="D105" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="E105" s="28" t="s">
         <v>167</v>
-      </c>
-      <c r="D105" s="21" t="s">
-        <v>270</v>
-      </c>
-      <c r="E105" s="28" t="s">
-        <v>188</v>
       </c>
       <c r="F105" s="28">
         <v>1</v>
@@ -5362,19 +5356,19 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B106" s="21" t="s">
         <v>24</v>
       </c>
       <c r="C106" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="D106" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="E106" s="28" t="s">
         <v>167</v>
-      </c>
-      <c r="D106" s="21" t="s">
-        <v>271</v>
-      </c>
-      <c r="E106" s="28" t="s">
-        <v>188</v>
       </c>
       <c r="F106" s="28">
         <v>1</v>
@@ -5388,19 +5382,19 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B107" s="21" t="s">
         <v>24</v>
       </c>
       <c r="C107" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="D107" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="E107" s="28" t="s">
         <v>167</v>
-      </c>
-      <c r="D107" s="21" t="s">
-        <v>272</v>
-      </c>
-      <c r="E107" s="28" t="s">
-        <v>188</v>
       </c>
       <c r="F107" s="28">
         <v>1</v>
@@ -5414,19 +5408,19 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B108" s="22" t="s">
         <v>24</v>
       </c>
       <c r="C108" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="D108" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="E108" s="29" t="s">
         <v>167</v>
-      </c>
-      <c r="D108" s="22" t="s">
-        <v>273</v>
-      </c>
-      <c r="E108" s="29" t="s">
-        <v>188</v>
       </c>
       <c r="F108" s="29">
         <v>1</v>
@@ -5440,19 +5434,19 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B109" s="21" t="s">
         <v>25</v>
       </c>
       <c r="C109" s="21" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="D109" s="21" t="s">
-        <v>274</v>
+        <v>253</v>
       </c>
       <c r="E109" s="28" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="F109" s="28">
         <v>1</v>
@@ -5466,19 +5460,19 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B110" s="21" t="s">
         <v>25</v>
       </c>
       <c r="C110" s="21" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="D110" s="21" t="s">
-        <v>275</v>
+        <v>254</v>
       </c>
       <c r="E110" s="28" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="F110" s="28">
         <v>1</v>
@@ -5492,19 +5486,19 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B111" s="21" t="s">
         <v>25</v>
       </c>
       <c r="C111" s="21" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="D111" s="21" t="s">
-        <v>276</v>
+        <v>255</v>
       </c>
       <c r="E111" s="28" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="F111" s="28">
         <v>1</v>
@@ -5518,19 +5512,19 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B112" s="22" t="s">
         <v>25</v>
       </c>
       <c r="C112" s="22" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="D112" s="22" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
       <c r="E112" s="29" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="F112" s="29">
         <v>1</v>
@@ -5544,19 +5538,19 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="23" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B113" s="23" t="s">
-        <v>26</v>
+        <v>294</v>
       </c>
       <c r="C113" s="21" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="D113" s="23" t="s">
-        <v>76</v>
+        <v>295</v>
       </c>
       <c r="E113" s="30" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="F113" s="30">
         <v>0</v>
@@ -5570,19 +5564,19 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B114" s="21" t="s">
-        <v>26</v>
+        <v>294</v>
       </c>
       <c r="C114" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="D114" s="21" t="s">
-        <v>71</v>
+        <v>155</v>
+      </c>
+      <c r="D114" s="25" t="s">
+        <v>296</v>
       </c>
       <c r="E114" s="28" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="F114" s="28">
         <v>0</v>
@@ -5596,19 +5590,19 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B115" s="21" t="s">
-        <v>26</v>
+        <v>294</v>
       </c>
       <c r="C115" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="D115" s="21" t="s">
-        <v>72</v>
+        <v>155</v>
+      </c>
+      <c r="D115" s="25" t="s">
+        <v>297</v>
       </c>
       <c r="E115" s="28" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="F115" s="28">
         <v>0</v>
@@ -5622,19 +5616,19 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B116" s="21" t="s">
-        <v>26</v>
+        <v>294</v>
       </c>
       <c r="C116" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="D116" s="21" t="s">
-        <v>73</v>
+        <v>155</v>
+      </c>
+      <c r="D116" s="25" t="s">
+        <v>298</v>
       </c>
       <c r="E116" s="28" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="F116" s="28">
         <v>0</v>
@@ -5648,19 +5642,19 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B117" s="21" t="s">
-        <v>26</v>
+        <v>294</v>
       </c>
       <c r="C117" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="D117" s="21" t="s">
-        <v>74</v>
+        <v>155</v>
+      </c>
+      <c r="D117" s="25" t="s">
+        <v>299</v>
       </c>
       <c r="E117" s="28" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="F117" s="28">
         <v>0</v>
@@ -5674,19 +5668,19 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B118" s="21" t="s">
-        <v>26</v>
+        <v>294</v>
       </c>
       <c r="C118" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="D118" s="21" t="s">
-        <v>75</v>
+        <v>155</v>
+      </c>
+      <c r="D118" s="25" t="s">
+        <v>300</v>
       </c>
       <c r="E118" s="28" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="F118" s="28">
         <v>0</v>
@@ -5700,19 +5694,19 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="23" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B119" s="23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C119" s="23" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="D119" s="23" t="s">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="E119" s="30" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="F119" s="30">
         <v>0</v>
@@ -5726,19 +5720,19 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B120" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C120" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="D120" s="21" t="s">
-        <v>77</v>
+        <v>156</v>
+      </c>
+      <c r="D120" s="25" t="s">
+        <v>302</v>
       </c>
       <c r="E120" s="28" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="F120" s="28">
         <v>0</v>
@@ -5752,19 +5746,19 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B121" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C121" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="D121" s="21" t="s">
-        <v>78</v>
+        <v>156</v>
+      </c>
+      <c r="D121" s="25" t="s">
+        <v>303</v>
       </c>
       <c r="E121" s="28" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="F121" s="28">
         <v>0</v>
@@ -5778,19 +5772,19 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B122" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C122" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="D122" s="21" t="s">
-        <v>79</v>
+        <v>156</v>
+      </c>
+      <c r="D122" s="25" t="s">
+        <v>304</v>
       </c>
       <c r="E122" s="28" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="F122" s="28">
         <v>0</v>
@@ -5804,19 +5798,19 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B123" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C123" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="D123" s="21" t="s">
-        <v>80</v>
+        <v>156</v>
+      </c>
+      <c r="D123" s="25" t="s">
+        <v>305</v>
       </c>
       <c r="E123" s="28" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="F123" s="28">
         <v>0</v>
@@ -5830,19 +5824,19 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B124" s="22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C124" s="22" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="D124" s="22" t="s">
-        <v>81</v>
+        <v>306</v>
       </c>
       <c r="E124" s="29" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="F124" s="29">
         <v>0</v>
@@ -5856,19 +5850,19 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="23" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B125" s="23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C125" s="21" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="D125" s="23" t="s">
-        <v>88</v>
+        <v>307</v>
       </c>
       <c r="E125" s="30" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="F125" s="30">
         <v>0</v>
@@ -5882,19 +5876,19 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B126" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C126" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="D126" s="21" t="s">
-        <v>83</v>
+        <v>157</v>
+      </c>
+      <c r="D126" s="25" t="s">
+        <v>308</v>
       </c>
       <c r="E126" s="28" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="F126" s="28">
         <v>0</v>
@@ -5908,19 +5902,19 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B127" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C127" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="D127" s="21" t="s">
-        <v>84</v>
+        <v>157</v>
+      </c>
+      <c r="D127" s="25" t="s">
+        <v>309</v>
       </c>
       <c r="E127" s="28" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="F127" s="28">
         <v>0</v>
@@ -5934,19 +5928,19 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B128" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C128" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="D128" s="21" t="s">
-        <v>85</v>
+        <v>157</v>
+      </c>
+      <c r="D128" s="25" t="s">
+        <v>310</v>
       </c>
       <c r="E128" s="28" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="F128" s="28">
         <v>0</v>
@@ -5960,19 +5954,19 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B129" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C129" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="D129" s="21" t="s">
-        <v>86</v>
+        <v>157</v>
+      </c>
+      <c r="D129" s="25" t="s">
+        <v>311</v>
       </c>
       <c r="E129" s="28" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="F129" s="28">
         <v>0</v>
@@ -5986,19 +5980,19 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B130" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C130" s="22" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="D130" s="22" t="s">
-        <v>87</v>
+        <v>312</v>
       </c>
       <c r="E130" s="29" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="F130" s="29">
         <v>0</v>
@@ -6012,19 +6006,19 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" s="23" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B131" s="23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C131" s="21" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="D131" s="23" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="E131" s="30" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="F131" s="30">
         <v>0</v>
@@ -6038,19 +6032,19 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B132" s="21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C132" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="D132" s="21" t="s">
-        <v>89</v>
+        <v>158</v>
+      </c>
+      <c r="D132" s="25" t="s">
+        <v>69</v>
       </c>
       <c r="E132" s="28" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="F132" s="28">
         <v>0</v>
@@ -6064,19 +6058,19 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B133" s="21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C133" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="D133" s="21" t="s">
-        <v>90</v>
+        <v>158</v>
+      </c>
+      <c r="D133" s="25" t="s">
+        <v>70</v>
       </c>
       <c r="E133" s="28" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="F133" s="28">
         <v>0</v>
@@ -6090,19 +6084,19 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B134" s="21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C134" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="D134" s="21" t="s">
-        <v>91</v>
+        <v>158</v>
+      </c>
+      <c r="D134" s="25" t="s">
+        <v>71</v>
       </c>
       <c r="E134" s="28" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="F134" s="28">
         <v>0</v>
@@ -6116,19 +6110,19 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B135" s="21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C135" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="D135" s="21" t="s">
-        <v>92</v>
+        <v>158</v>
+      </c>
+      <c r="D135" s="25" t="s">
+        <v>72</v>
       </c>
       <c r="E135" s="28" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="F135" s="28">
         <v>0</v>
@@ -6142,19 +6136,19 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B136" s="22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C136" s="22" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="D136" s="22" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="E136" s="29" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="F136" s="29">
         <v>0</v>
@@ -6168,19 +6162,19 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B137" s="21" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="C137" s="25" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="D137" s="49" t="s">
-        <v>299</v>
+        <v>278</v>
       </c>
       <c r="E137" s="28" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="F137" s="45">
         <v>0</v>
@@ -6194,19 +6188,19 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B138" s="21" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="C138" s="25" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="D138" s="21" t="s">
-        <v>300</v>
+        <v>279</v>
       </c>
       <c r="E138" s="28" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="F138" s="45">
         <v>0</v>
@@ -6220,19 +6214,19 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B139" s="21" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="C139" s="25" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="D139" s="21" t="s">
-        <v>301</v>
+        <v>280</v>
       </c>
       <c r="E139" s="28" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="F139" s="45">
         <v>0</v>
@@ -6246,19 +6240,19 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B140" s="21" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="C140" s="21" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="D140" s="21" t="s">
-        <v>302</v>
+        <v>281</v>
       </c>
       <c r="E140" s="28" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="F140" s="45">
         <v>0</v>
@@ -6272,19 +6266,19 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" s="22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B141" s="22" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="C141" s="22" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="D141" s="50" t="s">
-        <v>303</v>
+        <v>282</v>
       </c>
       <c r="E141" s="29" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="F141" s="46">
         <v>0</v>
@@ -6298,16 +6292,16 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B142" s="21" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
       <c r="C142" s="25" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="D142" s="49" t="s">
-        <v>304</v>
+        <v>283</v>
       </c>
       <c r="E142" s="45"/>
       <c r="F142" s="45">
@@ -6322,16 +6316,16 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B143" s="21" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
       <c r="C143" s="25" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="D143" s="21" t="s">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="E143" s="45"/>
       <c r="F143" s="45">
@@ -6346,16 +6340,16 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B144" s="21" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
       <c r="C144" s="25" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="D144" s="21" t="s">
-        <v>306</v>
+        <v>285</v>
       </c>
       <c r="E144" s="45"/>
       <c r="F144" s="45">
@@ -6370,16 +6364,16 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B145" s="21" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
       <c r="C145" s="21" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="D145" s="21" t="s">
-        <v>307</v>
+        <v>286</v>
       </c>
       <c r="E145" s="45"/>
       <c r="F145" s="45">
@@ -6394,16 +6388,16 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B146" s="22" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
       <c r="C146" s="22" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="D146" s="50" t="s">
-        <v>308</v>
+        <v>287</v>
       </c>
       <c r="E146" s="46"/>
       <c r="F146" s="46">
@@ -6418,16 +6412,16 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B147" s="21" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="C147" s="25" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="D147" s="49" t="s">
-        <v>309</v>
+        <v>288</v>
       </c>
       <c r="E147" s="45"/>
       <c r="F147" s="45">
@@ -6442,16 +6436,16 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B148" s="21" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="C148" s="25" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="D148" s="21" t="s">
-        <v>310</v>
+        <v>289</v>
       </c>
       <c r="E148" s="45"/>
       <c r="F148" s="45">
@@ -6466,16 +6460,16 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B149" s="21" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="C149" s="25" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="D149" s="21" t="s">
-        <v>311</v>
+        <v>290</v>
       </c>
       <c r="E149" s="45"/>
       <c r="F149" s="45">
@@ -6490,16 +6484,16 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B150" s="21" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="C150" s="21" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="D150" s="21" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="E150" s="45"/>
       <c r="F150" s="45">
@@ -6514,16 +6508,16 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B151" s="22" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="C151" s="22" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="D151" s="50" t="s">
-        <v>313</v>
+        <v>292</v>
       </c>
       <c r="E151" s="46"/>
       <c r="F151" s="46">
@@ -6538,19 +6532,19 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B152" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C152" s="25" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="D152" s="21" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="E152" s="28" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="F152" s="28">
         <v>0</v>
@@ -6564,19 +6558,19 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B153" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C153" s="21" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="D153" s="21" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E153" s="28" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="F153" s="28">
         <v>0</v>
@@ -6590,19 +6584,19 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" s="22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B154" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C154" s="22" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="D154" s="22" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="E154" s="29" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="F154" s="29">
         <v>0</v>
@@ -6616,19 +6610,19 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B155" s="21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C155" s="25" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="D155" s="21" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="E155" s="28" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="F155" s="28">
         <v>0</v>
@@ -6642,19 +6636,19 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B156" s="21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C156" s="25" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="D156" s="21" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="E156" s="28" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="F156" s="28">
         <v>0</v>
@@ -6668,19 +6662,19 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" s="22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B157" s="22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C157" s="22" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="D157" s="22" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E157" s="29" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="F157" s="29">
         <v>0</v>
@@ -6694,19 +6688,19 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B158" s="21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C158" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="D158" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="E158" s="28" t="s">
         <v>171</v>
-      </c>
-      <c r="D158" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="E158" s="28" t="s">
-        <v>192</v>
       </c>
       <c r="F158" s="28">
         <v>1</v>
@@ -6720,19 +6714,19 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B159" s="21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C159" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="D159" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="E159" s="28" t="s">
         <v>171</v>
-      </c>
-      <c r="D159" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="E159" s="28" t="s">
-        <v>192</v>
       </c>
       <c r="F159" s="28">
         <v>1</v>
@@ -6746,19 +6740,19 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B160" s="21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C160" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="D160" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="E160" s="28" t="s">
         <v>171</v>
-      </c>
-      <c r="D160" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="E160" s="28" t="s">
-        <v>192</v>
       </c>
       <c r="F160" s="28">
         <v>1</v>
@@ -6772,19 +6766,19 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" s="21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B161" s="21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C161" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="D161" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="E161" s="28" t="s">
         <v>171</v>
-      </c>
-      <c r="D161" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="E161" s="28" t="s">
-        <v>192</v>
       </c>
       <c r="F161" s="28">
         <v>1</v>
@@ -6798,19 +6792,19 @@
     </row>
     <row r="162" spans="1:8" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="24" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B162" s="24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C162" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="D162" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="E162" s="31" t="s">
         <v>171</v>
-      </c>
-      <c r="D162" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="E162" s="31" t="s">
-        <v>192</v>
       </c>
       <c r="F162" s="31">
         <v>1</v>

--- a/data-workflow/raw-data/mim_variables.xlsx
+++ b/data-workflow/raw-data/mim_variables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\este.de.ahora\Documents\_investigacion\00_Doctorado\00_Tesis-PhD\PhD\data-workflow\raw-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D9E3996-4EE8-4128-828D-DECA4184931D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C52018F-224C-4C3A-A2DE-F47BD7C4CDA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" activeTab="1" xr2:uid="{DF7805F5-E45D-47F7-961F-4760F5F8126C}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="CAT" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CAT!$A$1:$H$162</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">CAT!$A$1:$H$166</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <webPublishing allowPng="1" targetScreenSize="1024x768" codePage="65001"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1097" uniqueCount="319">
   <si>
     <t>Nivel</t>
   </si>
@@ -290,9 +290,6 @@
     <t>inSEG_Q5</t>
   </si>
   <si>
-    <t>Trabajo</t>
-  </si>
-  <si>
     <t>Estudio</t>
   </si>
   <si>
@@ -653,51 +650,6 @@
     <t>rSEGRES_Q5</t>
   </si>
   <si>
-    <t>rPRI_%[1,22]</t>
-  </si>
-  <si>
-    <t>rPRI_%(22,36]</t>
-  </si>
-  <si>
-    <t>rPRI_%(36,54]</t>
-  </si>
-  <si>
-    <t>rPRI_%(54,69]</t>
-  </si>
-  <si>
-    <t>rPRI_%(69,95]</t>
-  </si>
-  <si>
-    <t>rSEC_%[0,26]</t>
-  </si>
-  <si>
-    <t>rSEC_%(26,32]</t>
-  </si>
-  <si>
-    <t>rSEC_%(32,37]</t>
-  </si>
-  <si>
-    <t>rSEC_%(37,41]</t>
-  </si>
-  <si>
-    <t>rSEC_%(41,70]</t>
-  </si>
-  <si>
-    <t>rSUP_%[0,4]</t>
-  </si>
-  <si>
-    <t>rSUP_%(4,12]</t>
-  </si>
-  <si>
-    <t>rSUP_%(12,23]</t>
-  </si>
-  <si>
-    <t>rSUP_%(23,38]</t>
-  </si>
-  <si>
-    <t>rSUP_%(38,88]</t>
-  </si>
-  <si>
     <t>rLON_Oeste</t>
   </si>
   <si>
@@ -803,21 +755,6 @@
     <t>inSUP_%(43,100]</t>
   </si>
   <si>
-    <t>vDIFSEG_MBajo</t>
-  </si>
-  <si>
-    <t>vDIFSEG_Bajo</t>
-  </si>
-  <si>
-    <t>vDIFSEG_IGUAL</t>
-  </si>
-  <si>
-    <t>vDIFSEG_Alto</t>
-  </si>
-  <si>
-    <t>vDIFSEG_MAlto</t>
-  </si>
-  <si>
     <t>vDistVia_barrial</t>
   </si>
   <si>
@@ -969,6 +906,87 @@
   </si>
   <si>
     <t>inRec_Q5</t>
+  </si>
+  <si>
+    <t>rPRI%[1,22]</t>
+  </si>
+  <si>
+    <t>rPRI%(22,36]</t>
+  </si>
+  <si>
+    <t>rPRI%(36,54]</t>
+  </si>
+  <si>
+    <t>rPRI%(54,69]</t>
+  </si>
+  <si>
+    <t>rPRI%(69,95]</t>
+  </si>
+  <si>
+    <t>rSEC%[0,26]</t>
+  </si>
+  <si>
+    <t>rSEC%(26,32]</t>
+  </si>
+  <si>
+    <t>rSEC%(32,37]</t>
+  </si>
+  <si>
+    <t>rSEC%(37,41]</t>
+  </si>
+  <si>
+    <t>rSEC%(41,70]</t>
+  </si>
+  <si>
+    <t>rSUP%[0,4]</t>
+  </si>
+  <si>
+    <t>rSUP%(4,12]</t>
+  </si>
+  <si>
+    <t>rSUP%(12,23]</t>
+  </si>
+  <si>
+    <t>rSUP%(23,38]</t>
+  </si>
+  <si>
+    <t>rSUP%(38,88]</t>
+  </si>
+  <si>
+    <t>Laboral</t>
+  </si>
+  <si>
+    <t>Centralidad. Distancia a Plaza de Mayo (CABA)</t>
+  </si>
+  <si>
+    <t>Distancia del lugar de actividad respecto a la ubicación de la residencia</t>
+  </si>
+  <si>
+    <t>inDistRes_barrial</t>
+  </si>
+  <si>
+    <t>inDistRes_1a10km</t>
+  </si>
+  <si>
+    <t>inDistRes_10a25km</t>
+  </si>
+  <si>
+    <t>inDistRes_mas25km</t>
+  </si>
+  <si>
+    <t>vDIFSEG_DES++</t>
+  </si>
+  <si>
+    <t>vDIFSEG_DES+</t>
+  </si>
+  <si>
+    <t>vDIFSEG_=</t>
+  </si>
+  <si>
+    <t>vDIFSEG_RES+</t>
+  </si>
+  <si>
+    <t>vDIFSEG_RES++</t>
   </si>
 </sst>
 </file>
@@ -1136,7 +1154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1275,6 +1293,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1575,16 +1596,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>36</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.95" x14ac:dyDescent="0.25">
@@ -1624,7 +1645,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C4" s="37" t="s">
         <v>4</v>
@@ -1638,7 +1659,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C5" s="39" t="s">
         <v>5</v>
@@ -1683,7 +1704,7 @@
         <v>4</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>42</v>
@@ -1703,7 +1724,7 @@
         <v>2</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>42</v>
@@ -1734,10 +1755,10 @@
         <v>35</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D10" s="11">
         <v>5</v>
@@ -1757,7 +1778,7 @@
         <v>46</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D11" s="11">
         <v>5</v>
@@ -1777,7 +1798,7 @@
         <v>47</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D12" s="11">
         <v>5</v>
@@ -1797,7 +1818,7 @@
         <v>48</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D13" s="11">
         <v>5</v>
@@ -1814,10 +1835,10 @@
         <v>35</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C14" s="40" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D14" s="11">
         <v>5</v>
@@ -1826,7 +1847,7 @@
         <v>40</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="14.3" customHeight="1" x14ac:dyDescent="0.25">
@@ -1834,10 +1855,10 @@
         <v>35</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C15" s="40" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D15" s="11">
         <v>5</v>
@@ -1846,7 +1867,7 @@
         <v>40</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="14.95" x14ac:dyDescent="0.25">
@@ -1854,7 +1875,7 @@
         <v>35</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C16" s="37" t="s">
         <v>10</v>
@@ -1874,7 +1895,7 @@
         <v>35</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C17" s="37" t="s">
         <v>11</v>
@@ -1894,14 +1915,14 @@
         <v>35</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D18" s="15"/>
       <c r="E18" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F18" s="13" t="s">
         <v>49</v>
@@ -1915,11 +1936,11 @@
         <v>46</v>
       </c>
       <c r="C19" s="36" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F19" s="13" t="s">
         <v>49</v>
@@ -1933,11 +1954,11 @@
         <v>47</v>
       </c>
       <c r="C20" s="36" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D20" s="15"/>
       <c r="E20" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F20" s="13" t="s">
         <v>49</v>
@@ -1951,11 +1972,11 @@
         <v>48</v>
       </c>
       <c r="C21" s="41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D21" s="18"/>
       <c r="E21" s="18" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F21" s="16" t="s">
         <v>49</v>
@@ -1966,7 +1987,7 @@
         <v>38</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C22" s="37" t="s">
         <v>33</v>
@@ -1986,10 +2007,10 @@
         <v>38</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C23" s="37" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D23" s="11">
         <v>5</v>
@@ -2006,10 +2027,10 @@
         <v>38</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C24" s="40" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D24" s="11">
         <v>5</v>
@@ -2026,10 +2047,10 @@
         <v>38</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C25" s="40" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D25" s="11">
         <v>5</v>
@@ -2038,7 +2059,7 @@
         <v>40</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2046,14 +2067,14 @@
         <v>38</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C26" s="37" t="s">
         <v>34</v>
       </c>
       <c r="D26" s="15"/>
       <c r="E26" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F26" s="13" t="s">
         <v>42</v>
@@ -2064,14 +2085,14 @@
         <v>38</v>
       </c>
       <c r="B27" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="C27" s="40" t="s">
         <v>190</v>
-      </c>
-      <c r="C27" s="40" t="s">
-        <v>191</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>49</v>
@@ -2082,17 +2103,17 @@
         <v>38</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C28" s="40" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D28" s="15"/>
       <c r="E28" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2112,7 +2133,7 @@
         <v>40</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -2120,10 +2141,10 @@
         <v>37</v>
       </c>
       <c r="B30" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="C30" s="40" t="s">
         <v>196</v>
-      </c>
-      <c r="C30" s="40" t="s">
-        <v>197</v>
       </c>
       <c r="D30" s="11">
         <v>4</v>
@@ -2132,7 +2153,7 @@
         <v>40</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2140,10 +2161,10 @@
         <v>37</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C31" s="52" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="D31" s="11">
         <v>5</v>
@@ -2160,7 +2181,7 @@
         <v>37</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C32" s="37" t="s">
         <v>21</v>
@@ -2180,7 +2201,7 @@
         <v>37</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C33" s="37" t="s">
         <v>22</v>
@@ -2200,7 +2221,7 @@
         <v>37</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C34" s="37" t="s">
         <v>23</v>
@@ -2220,7 +2241,7 @@
         <v>37</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C35" s="37" t="s">
         <v>24</v>
@@ -2240,7 +2261,7 @@
         <v>37</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C36" s="37" t="s">
         <v>25</v>
@@ -2255,15 +2276,15 @@
         <v>42</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C37" s="37" t="s">
-        <v>294</v>
+        <v>273</v>
       </c>
       <c r="D37" s="11">
         <v>6</v>
@@ -2280,7 +2301,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C38" s="37" t="s">
         <v>26</v>
@@ -2295,12 +2316,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="42.8" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C39" s="37" t="s">
         <v>27</v>
@@ -2315,12 +2336,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C40" s="37" t="s">
         <v>28</v>
@@ -2340,7 +2361,7 @@
         <v>37</v>
       </c>
       <c r="B41" s="43" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C41" s="37" t="s">
         <v>32</v>
@@ -2360,10 +2381,10 @@
         <v>37</v>
       </c>
       <c r="B42" s="43" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C42" s="40" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D42" s="11">
         <v>5</v>
@@ -2380,10 +2401,10 @@
         <v>37</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C43" s="40" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D43" s="11">
         <v>5</v>
@@ -2392,7 +2413,7 @@
         <v>40</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="14.3" customHeight="1" x14ac:dyDescent="0.25">
@@ -2400,10 +2421,10 @@
         <v>37</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C44" s="40" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D44" s="11">
         <v>5</v>
@@ -2412,7 +2433,7 @@
         <v>40</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2420,7 +2441,7 @@
         <v>37</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C45" s="37" t="s">
         <v>29</v>
@@ -2435,12 +2456,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="14.95" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C46" s="37" t="s">
         <v>30</v>
@@ -2460,17 +2481,17 @@
         <v>37</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C47" s="37" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D47" s="15"/>
       <c r="E47" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2478,14 +2499,14 @@
         <v>37</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C48" s="37" t="s">
-        <v>293</v>
+        <v>272</v>
       </c>
       <c r="D48" s="15"/>
       <c r="E48" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F48" s="13" t="s">
         <v>42</v>
@@ -2496,14 +2517,14 @@
         <v>37</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C49" s="37" t="s">
         <v>16</v>
       </c>
       <c r="D49" s="15"/>
       <c r="E49" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F49" s="13"/>
     </row>
@@ -2512,14 +2533,14 @@
         <v>37</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C50" s="37" t="s">
         <v>17</v>
       </c>
       <c r="D50" s="15"/>
       <c r="E50" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F50" s="13"/>
     </row>
@@ -2528,14 +2549,14 @@
         <v>37</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C51" s="37" t="s">
         <v>18</v>
       </c>
       <c r="D51" s="15"/>
       <c r="E51" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F51" s="13"/>
     </row>
@@ -2544,14 +2565,14 @@
         <v>37</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C52" s="37" t="s">
         <v>19</v>
       </c>
       <c r="D52" s="15"/>
       <c r="E52" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F52" s="13"/>
     </row>
@@ -2560,14 +2581,14 @@
         <v>37</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C53" s="37" t="s">
         <v>20</v>
       </c>
       <c r="D53" s="15"/>
       <c r="E53" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F53" s="13"/>
     </row>
@@ -2576,14 +2597,14 @@
         <v>37</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C54" s="37" t="s">
         <v>31</v>
       </c>
       <c r="D54" s="15"/>
       <c r="E54" s="15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F54" s="13"/>
     </row>
@@ -2592,14 +2613,14 @@
         <v>37</v>
       </c>
       <c r="B55" s="17" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C55" s="41" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D55" s="18"/>
       <c r="E55" s="18" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F55" s="16"/>
     </row>
@@ -2611,7 +2632,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I163"/>
+  <dimension ref="A1:I167"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.25" customWidth="1"/>
@@ -2627,25 +2648,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="F1" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="G1" s="26" t="s">
+        <v>163</v>
+      </c>
+      <c r="H1" s="26" t="s">
         <v>107</v>
-      </c>
-      <c r="C1" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="D1" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="E1" s="26" t="s">
-        <v>160</v>
-      </c>
-      <c r="F1" s="26" t="s">
-        <v>159</v>
-      </c>
-      <c r="G1" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="14.95" thickTop="1" x14ac:dyDescent="0.25">
@@ -2659,10 +2680,10 @@
         <v>39</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E2" s="32" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F2" s="32">
         <v>1</v>
@@ -2685,10 +2706,10 @@
         <v>39</v>
       </c>
       <c r="D3" s="25" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F3" s="32">
         <v>1</v>
@@ -2711,10 +2732,10 @@
         <v>39</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F4" s="32">
         <v>1</v>
@@ -2737,10 +2758,10 @@
         <v>39</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F5" s="32">
         <v>1</v>
@@ -2763,10 +2784,10 @@
         <v>39</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F6" s="32">
         <v>1</v>
@@ -2789,10 +2810,10 @@
         <v>39</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F7" s="32">
         <v>1</v>
@@ -2815,10 +2836,10 @@
         <v>39</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F8" s="32">
         <v>1</v>
@@ -2841,10 +2862,10 @@
         <v>39</v>
       </c>
       <c r="D9" s="25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F9" s="32">
         <v>1</v>
@@ -2867,10 +2888,10 @@
         <v>39</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F10" s="29">
         <v>1</v>
@@ -2890,13 +2911,13 @@
         <v>7</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E11" s="32" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F11" s="32">
         <v>0</v>
@@ -2916,13 +2937,13 @@
         <v>7</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E12" s="32" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F12" s="32">
         <v>0</v>
@@ -2942,13 +2963,13 @@
         <v>7</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F13" s="28">
         <v>0</v>
@@ -2968,13 +2989,13 @@
         <v>7</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E14" s="29" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F14" s="29">
         <v>0</v>
@@ -2994,13 +3015,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E15" s="32" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F15" s="32">
         <v>0</v>
@@ -3020,13 +3041,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F16" s="29">
         <v>0</v>
@@ -3046,13 +3067,13 @@
         <v>9</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E17" s="32" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F17" s="32">
         <v>0</v>
@@ -3072,13 +3093,13 @@
         <v>9</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E18" s="32" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F18" s="32">
         <v>0</v>
@@ -3098,13 +3119,13 @@
         <v>9</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E19" s="29" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F19" s="29">
         <v>0</v>
@@ -3121,19 +3142,19 @@
         <v>35</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E20" s="32" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F20" s="32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="32">
         <v>0</v>
@@ -3147,19 +3168,19 @@
         <v>35</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D21" s="25" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E21" s="32" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F21" s="32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" s="32">
         <v>0</v>
@@ -3173,19 +3194,19 @@
         <v>35</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D22" s="25" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E22" s="32" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F22" s="32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" s="32">
         <v>0</v>
@@ -3199,19 +3220,19 @@
         <v>35</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E23" s="28" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F23" s="28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="28">
         <v>0</v>
@@ -3225,19 +3246,19 @@
         <v>35</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E24" s="29" t="s">
-        <v>172</v>
-      </c>
-      <c r="F24" s="29">
-        <v>0</v>
+        <v>171</v>
+      </c>
+      <c r="F24" s="54">
+        <v>1</v>
       </c>
       <c r="G24" s="29">
         <v>0</v>
@@ -3254,13 +3275,13 @@
         <v>12</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D25" s="25" t="s">
-        <v>207</v>
+        <v>292</v>
       </c>
       <c r="E25" s="32" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F25" s="32">
         <v>1</v>
@@ -3280,13 +3301,13 @@
         <v>12</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D26" s="25" t="s">
-        <v>208</v>
+        <v>293</v>
       </c>
       <c r="E26" s="32" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F26" s="32">
         <v>1</v>
@@ -3306,13 +3327,13 @@
         <v>12</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D27" s="25" t="s">
-        <v>209</v>
+        <v>294</v>
       </c>
       <c r="E27" s="32" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F27" s="32">
         <v>1</v>
@@ -3332,13 +3353,13 @@
         <v>12</v>
       </c>
       <c r="C28" s="25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>210</v>
+        <v>295</v>
       </c>
       <c r="E28" s="32" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F28" s="32">
         <v>1</v>
@@ -3358,13 +3379,13 @@
         <v>12</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D29" s="22" t="s">
-        <v>211</v>
+        <v>296</v>
       </c>
       <c r="E29" s="29" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F29" s="29">
         <v>1</v>
@@ -3384,13 +3405,13 @@
         <v>13</v>
       </c>
       <c r="C30" s="25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D30" s="25" t="s">
-        <v>212</v>
+        <v>297</v>
       </c>
       <c r="E30" s="32" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F30" s="32">
         <v>1</v>
@@ -3410,13 +3431,13 @@
         <v>13</v>
       </c>
       <c r="C31" s="25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D31" s="25" t="s">
-        <v>213</v>
+        <v>298</v>
       </c>
       <c r="E31" s="32" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F31" s="32">
         <v>1</v>
@@ -3436,13 +3457,13 @@
         <v>13</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D32" s="25" t="s">
-        <v>214</v>
+        <v>299</v>
       </c>
       <c r="E32" s="32" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F32" s="32">
         <v>1</v>
@@ -3462,13 +3483,13 @@
         <v>13</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D33" s="25" t="s">
-        <v>215</v>
+        <v>300</v>
       </c>
       <c r="E33" s="32" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F33" s="32">
         <v>1</v>
@@ -3488,13 +3509,13 @@
         <v>13</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D34" s="22" t="s">
-        <v>216</v>
+        <v>301</v>
       </c>
       <c r="E34" s="29" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F34" s="29">
         <v>1</v>
@@ -3514,13 +3535,13 @@
         <v>14</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>217</v>
+        <v>302</v>
       </c>
       <c r="E35" s="32" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F35" s="32">
         <v>1</v>
@@ -3540,13 +3561,13 @@
         <v>14</v>
       </c>
       <c r="C36" s="25" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D36" s="25" t="s">
-        <v>218</v>
+        <v>303</v>
       </c>
       <c r="E36" s="32" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F36" s="32">
         <v>1</v>
@@ -3566,13 +3587,13 @@
         <v>14</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D37" s="25" t="s">
-        <v>219</v>
+        <v>304</v>
       </c>
       <c r="E37" s="32" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F37" s="32">
         <v>1</v>
@@ -3592,13 +3613,13 @@
         <v>14</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>220</v>
+        <v>305</v>
       </c>
       <c r="E38" s="28" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F38" s="28">
         <v>1</v>
@@ -3618,13 +3639,13 @@
         <v>14</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D39" s="22" t="s">
-        <v>221</v>
+        <v>306</v>
       </c>
       <c r="E39" s="29" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F39" s="29">
         <v>1</v>
@@ -3641,25 +3662,25 @@
         <v>35</v>
       </c>
       <c r="B40" s="25" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C40" s="25" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D40" s="25" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="E40" s="32" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F40" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" s="44">
         <v>0</v>
       </c>
       <c r="H40" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -3667,25 +3688,25 @@
         <v>35</v>
       </c>
       <c r="B41" s="21" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D41" s="21" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="E41" s="28" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F41" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" s="45">
         <v>0</v>
       </c>
       <c r="H41" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -3693,25 +3714,25 @@
         <v>35</v>
       </c>
       <c r="B42" s="21" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D42" s="21" t="s">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="E42" s="28" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F42" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" s="45">
         <v>0</v>
       </c>
       <c r="H42" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -3719,25 +3740,25 @@
         <v>35</v>
       </c>
       <c r="B43" s="21" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D43" s="21" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="E43" s="28" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F43" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" s="45">
         <v>0</v>
       </c>
       <c r="H43" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -3745,25 +3766,25 @@
         <v>35</v>
       </c>
       <c r="B44" s="22" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C44" s="22" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D44" s="22" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="E44" s="29" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F44" s="46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" s="46">
         <v>0</v>
       </c>
       <c r="H44" s="46">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -3771,25 +3792,25 @@
         <v>35</v>
       </c>
       <c r="B45" s="25" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C45" s="25" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D45" s="25" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="E45" s="32" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F45" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" s="44">
         <v>0</v>
       </c>
       <c r="H45" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -3797,25 +3818,25 @@
         <v>35</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D46" s="21" t="s">
-        <v>234</v>
+        <v>218</v>
       </c>
       <c r="E46" s="28" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F46" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" s="45">
         <v>0</v>
       </c>
       <c r="H46" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -3823,25 +3844,25 @@
         <v>35</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C47" s="21" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D47" s="21" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="E47" s="28" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F47" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47" s="45">
         <v>0</v>
       </c>
       <c r="H47" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -3849,25 +3870,25 @@
         <v>35</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D48" s="21" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="E48" s="28" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F48" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" s="45">
         <v>0</v>
       </c>
       <c r="H48" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
@@ -3875,25 +3896,25 @@
         <v>35</v>
       </c>
       <c r="B49" s="22" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D49" s="22" t="s">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="E49" s="29" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F49" s="46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" s="46">
         <v>0</v>
       </c>
       <c r="H49" s="46">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -3904,13 +3925,13 @@
         <v>10</v>
       </c>
       <c r="C50" s="25" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D50" s="25" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="E50" s="28" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F50" s="32">
         <v>0</v>
@@ -3930,13 +3951,13 @@
         <v>10</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D51" s="21" t="s">
-        <v>223</v>
+        <v>207</v>
       </c>
       <c r="E51" s="28" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F51" s="28">
         <v>0</v>
@@ -3956,13 +3977,13 @@
         <v>10</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D52" s="22" t="s">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="E52" s="29" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F52" s="29">
         <v>0</v>
@@ -3982,13 +4003,13 @@
         <v>11</v>
       </c>
       <c r="C53" s="25" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D53" s="25" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="E53" s="28" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F53" s="32">
         <v>0</v>
@@ -4008,13 +4029,13 @@
         <v>11</v>
       </c>
       <c r="C54" s="25" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D54" s="25" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="E54" s="28" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F54" s="32">
         <v>0</v>
@@ -4034,13 +4055,13 @@
         <v>11</v>
       </c>
       <c r="C55" s="22" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D55" s="22" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="E55" s="29" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F55" s="29">
         <v>0</v>
@@ -4060,13 +4081,13 @@
         <v>33</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D56" s="33" t="s">
-        <v>86</v>
+        <v>307</v>
       </c>
       <c r="E56" s="34" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F56" s="34">
         <v>1</v>
@@ -4078,7 +4099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="14.95" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="21" t="s">
         <v>38</v>
       </c>
@@ -4086,13 +4107,13 @@
         <v>33</v>
       </c>
       <c r="C57" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D57" s="21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E57" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F57" s="28">
         <v>1</v>
@@ -4112,13 +4133,13 @@
         <v>33</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E58" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F58" s="28">
         <v>1</v>
@@ -4138,13 +4159,13 @@
         <v>33</v>
       </c>
       <c r="C59" s="22" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D59" s="22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E59" s="29" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F59" s="29">
         <v>1</v>
@@ -4161,16 +4182,16 @@
         <v>38</v>
       </c>
       <c r="B60" s="21" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D60" s="21" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="E60" s="28" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F60" s="28">
         <v>1</v>
@@ -4182,21 +4203,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="14.95" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="21" t="s">
         <v>38</v>
       </c>
       <c r="B61" s="21" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C61" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D61" s="21" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
       <c r="E61" s="28" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F61" s="28">
         <v>1</v>
@@ -4208,21 +4229,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="14.95" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="21" t="s">
         <v>38</v>
       </c>
       <c r="B62" s="21" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C62" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D62" s="21" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="E62" s="28" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F62" s="28">
         <v>1</v>
@@ -4239,16 +4260,16 @@
         <v>38</v>
       </c>
       <c r="B63" s="21" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C63" s="21" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D63" s="21" t="s">
-        <v>270</v>
+        <v>249</v>
       </c>
       <c r="E63" s="28" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F63" s="28">
         <v>1</v>
@@ -4265,16 +4286,16 @@
         <v>38</v>
       </c>
       <c r="B64" s="22" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C64" s="22" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D64" s="22" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="E64" s="29" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F64" s="29">
         <v>1</v>
@@ -4292,25 +4313,25 @@
         <v>38</v>
       </c>
       <c r="B65" s="21" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C65" s="21" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D65" s="49" t="s">
-        <v>257</v>
+        <v>318</v>
       </c>
       <c r="E65" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F65" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" s="45">
         <v>0</v>
       </c>
       <c r="H65" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
@@ -4318,25 +4339,25 @@
         <v>38</v>
       </c>
       <c r="B66" s="21" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C66" s="21" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D66" s="21" t="s">
-        <v>258</v>
+        <v>317</v>
       </c>
       <c r="E66" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F66" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" s="45">
         <v>0</v>
       </c>
       <c r="H66" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
@@ -4344,25 +4365,25 @@
         <v>38</v>
       </c>
       <c r="B67" s="21" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C67" s="21" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D67" s="21" t="s">
-        <v>259</v>
+        <v>316</v>
       </c>
       <c r="E67" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F67" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" s="45">
         <v>0</v>
       </c>
       <c r="H67" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
@@ -4370,25 +4391,25 @@
         <v>38</v>
       </c>
       <c r="B68" s="21" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C68" s="21" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D68" s="21" t="s">
-        <v>260</v>
+        <v>315</v>
       </c>
       <c r="E68" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F68" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" s="45">
         <v>0</v>
       </c>
       <c r="H68" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
@@ -4396,25 +4417,25 @@
         <v>38</v>
       </c>
       <c r="B69" s="22" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C69" s="22" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D69" s="50" t="s">
-        <v>261</v>
+        <v>314</v>
       </c>
       <c r="E69" s="29" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F69" s="46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" s="46">
         <v>0</v>
       </c>
       <c r="H69" s="46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" s="29"/>
     </row>
@@ -4423,25 +4444,25 @@
         <v>38</v>
       </c>
       <c r="B70" s="21" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C70" s="21" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D70" s="49" t="s">
-        <v>262</v>
+        <v>241</v>
       </c>
       <c r="E70" s="28" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F70" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70" s="45">
         <v>0</v>
       </c>
       <c r="H70" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
@@ -4449,25 +4470,25 @@
         <v>38</v>
       </c>
       <c r="B71" s="21" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C71" s="21" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D71" s="21" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="E71" s="28" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F71" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71" s="45">
         <v>0</v>
       </c>
       <c r="H71" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
@@ -4475,25 +4496,25 @@
         <v>38</v>
       </c>
       <c r="B72" s="21" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C72" s="21" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D72" s="21" t="s">
-        <v>264</v>
+        <v>243</v>
       </c>
       <c r="E72" s="28" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F72" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" s="45">
         <v>0</v>
       </c>
       <c r="H72" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
@@ -4501,25 +4522,25 @@
         <v>38</v>
       </c>
       <c r="B73" s="21" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C73" s="21" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D73" s="21" t="s">
-        <v>265</v>
+        <v>244</v>
       </c>
       <c r="E73" s="28" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F73" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73" s="45">
         <v>0</v>
       </c>
       <c r="H73" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
@@ -4527,16 +4548,16 @@
         <v>38</v>
       </c>
       <c r="B74" s="24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C74" s="24" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D74" s="51" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="E74" s="31" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F74" s="48">
         <v>0</v>
@@ -4556,13 +4577,13 @@
         <v>15</v>
       </c>
       <c r="C75" s="20" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D75" s="20" t="s">
         <v>55</v>
       </c>
       <c r="E75" s="27" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F75" s="27">
         <v>1</v>
@@ -4582,19 +4603,19 @@
         <v>15</v>
       </c>
       <c r="C76" s="21" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D76" s="21" t="s">
         <v>56</v>
       </c>
       <c r="E76" s="28" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F76" s="28">
         <v>1</v>
       </c>
       <c r="G76" s="32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76" s="28">
         <v>0</v>
@@ -4608,13 +4629,13 @@
         <v>15</v>
       </c>
       <c r="C77" s="21" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D77" s="21" t="s">
         <v>57</v>
       </c>
       <c r="E77" s="28" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F77" s="28">
         <v>1</v>
@@ -4634,13 +4655,13 @@
         <v>15</v>
       </c>
       <c r="C78" s="21" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D78" s="21" t="s">
         <v>58</v>
       </c>
       <c r="E78" s="28" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F78" s="28">
         <v>1</v>
@@ -4660,13 +4681,13 @@
         <v>15</v>
       </c>
       <c r="C79" s="21" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D79" s="21" t="s">
         <v>59</v>
       </c>
       <c r="E79" s="28" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F79" s="28">
         <v>1</v>
@@ -4686,13 +4707,13 @@
         <v>15</v>
       </c>
       <c r="C80" s="21" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D80" s="21" t="s">
         <v>60</v>
       </c>
       <c r="E80" s="28" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F80" s="28">
         <v>1</v>
@@ -4712,13 +4733,13 @@
         <v>15</v>
       </c>
       <c r="C81" s="21" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D81" s="21" t="s">
         <v>61</v>
       </c>
       <c r="E81" s="28" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F81" s="28">
         <v>1</v>
@@ -4738,13 +4759,13 @@
         <v>15</v>
       </c>
       <c r="C82" s="21" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D82" s="21" t="s">
         <v>62</v>
       </c>
       <c r="E82" s="28" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F82" s="28">
         <v>1</v>
@@ -4764,13 +4785,13 @@
         <v>15</v>
       </c>
       <c r="C83" s="22" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D83" s="22" t="s">
         <v>63</v>
       </c>
       <c r="E83" s="29" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F83" s="29">
         <v>1</v>
@@ -4787,19 +4808,19 @@
         <v>37</v>
       </c>
       <c r="B84" s="23" t="s">
-        <v>272</v>
+        <v>196</v>
       </c>
       <c r="C84" s="23" t="s">
-        <v>135</v>
+        <v>309</v>
       </c>
       <c r="D84" s="23" t="s">
-        <v>273</v>
+        <v>310</v>
       </c>
       <c r="E84" s="28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F84" s="53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" s="53">
         <v>0</v>
@@ -4813,19 +4834,19 @@
         <v>37</v>
       </c>
       <c r="B85" s="21" t="s">
-        <v>272</v>
+        <v>196</v>
       </c>
       <c r="C85" s="21" t="s">
-        <v>135</v>
+        <v>309</v>
       </c>
       <c r="D85" s="21" t="s">
-        <v>274</v>
+        <v>311</v>
       </c>
       <c r="E85" s="28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F85" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G85" s="45">
         <v>0</v>
@@ -4839,19 +4860,19 @@
         <v>37</v>
       </c>
       <c r="B86" s="21" t="s">
-        <v>272</v>
+        <v>196</v>
       </c>
       <c r="C86" s="21" t="s">
-        <v>135</v>
+        <v>309</v>
       </c>
       <c r="D86" s="21" t="s">
-        <v>275</v>
+        <v>312</v>
       </c>
       <c r="E86" s="28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F86" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G86" s="45">
         <v>0</v>
@@ -4861,54 +4882,54 @@
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B87" s="21" t="s">
-        <v>272</v>
-      </c>
-      <c r="C87" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="D87" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="E87" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="F87" s="45">
-        <v>0</v>
-      </c>
-      <c r="G87" s="45">
-        <v>0</v>
-      </c>
-      <c r="H87" s="45">
+      <c r="A87" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B87" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="C87" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="D87" s="22" t="s">
+        <v>313</v>
+      </c>
+      <c r="E87" s="29" t="s">
+        <v>172</v>
+      </c>
+      <c r="F87" s="46">
+        <v>1</v>
+      </c>
+      <c r="G87" s="46">
+        <v>0</v>
+      </c>
+      <c r="H87" s="46">
         <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="B88" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="C88" s="22" t="s">
-        <v>135</v>
-      </c>
-      <c r="D88" s="22" t="s">
-        <v>277</v>
-      </c>
-      <c r="E88" s="29" t="s">
-        <v>173</v>
-      </c>
-      <c r="F88" s="46">
-        <v>0</v>
-      </c>
-      <c r="G88" s="46">
-        <v>0</v>
-      </c>
-      <c r="H88" s="46">
+      <c r="A88" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="B88" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="C88" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="D88" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="E88" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="F88" s="53">
+        <v>1</v>
+      </c>
+      <c r="G88" s="53">
+        <v>0</v>
+      </c>
+      <c r="H88" s="53">
         <v>1</v>
       </c>
     </row>
@@ -4917,24 +4938,24 @@
         <v>37</v>
       </c>
       <c r="B89" s="21" t="s">
-        <v>21</v>
+        <v>251</v>
       </c>
       <c r="C89" s="21" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="D89" s="21" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="E89" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="F89" s="28">
-        <v>1</v>
-      </c>
-      <c r="G89" s="28">
-        <v>0</v>
-      </c>
-      <c r="H89" s="28">
+        <v>172</v>
+      </c>
+      <c r="F89" s="45">
+        <v>1</v>
+      </c>
+      <c r="G89" s="45">
+        <v>0</v>
+      </c>
+      <c r="H89" s="45">
         <v>1</v>
       </c>
     </row>
@@ -4943,24 +4964,24 @@
         <v>37</v>
       </c>
       <c r="B90" s="21" t="s">
-        <v>21</v>
+        <v>251</v>
       </c>
       <c r="C90" s="21" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="D90" s="21" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="E90" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="F90" s="28">
-        <v>1</v>
-      </c>
-      <c r="G90" s="28">
-        <v>0</v>
-      </c>
-      <c r="H90" s="28">
+        <v>172</v>
+      </c>
+      <c r="F90" s="45">
+        <v>1</v>
+      </c>
+      <c r="G90" s="45">
+        <v>0</v>
+      </c>
+      <c r="H90" s="45">
         <v>1</v>
       </c>
     </row>
@@ -4969,76 +4990,76 @@
         <v>37</v>
       </c>
       <c r="B91" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="C91" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="D91" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="E91" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="F91" s="45">
+        <v>1</v>
+      </c>
+      <c r="G91" s="45">
+        <v>0</v>
+      </c>
+      <c r="H91" s="45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B92" s="22" t="s">
+        <v>251</v>
+      </c>
+      <c r="C92" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="D92" s="22" t="s">
+        <v>256</v>
+      </c>
+      <c r="E92" s="29" t="s">
+        <v>172</v>
+      </c>
+      <c r="F92" s="46">
+        <v>1</v>
+      </c>
+      <c r="G92" s="46">
+        <v>0</v>
+      </c>
+      <c r="H92" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B93" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C91" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="D91" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="E91" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="F91" s="28">
-        <v>1</v>
-      </c>
-      <c r="G91" s="28">
-        <v>0</v>
-      </c>
-      <c r="H91" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B92" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C92" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="D92" s="21" t="s">
-        <v>241</v>
-      </c>
-      <c r="E92" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="F92" s="28">
-        <v>1</v>
-      </c>
-      <c r="G92" s="28">
-        <v>0</v>
-      </c>
-      <c r="H92" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="B93" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C93" s="22" t="s">
-        <v>143</v>
-      </c>
-      <c r="D93" s="22" t="s">
-        <v>242</v>
-      </c>
-      <c r="E93" s="29" t="s">
-        <v>173</v>
-      </c>
-      <c r="F93" s="29">
-        <v>1</v>
-      </c>
-      <c r="G93" s="29">
-        <v>0</v>
-      </c>
-      <c r="H93" s="29">
+      <c r="C93" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="D93" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="E93" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="F93" s="28">
+        <v>1</v>
+      </c>
+      <c r="G93" s="28">
+        <v>0</v>
+      </c>
+      <c r="H93" s="28">
         <v>1</v>
       </c>
     </row>
@@ -5047,22 +5068,22 @@
         <v>37</v>
       </c>
       <c r="B94" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C94" s="21" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D94" s="21" t="s">
-        <v>64</v>
+        <v>223</v>
       </c>
       <c r="E94" s="28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F94" s="28">
         <v>1</v>
       </c>
       <c r="G94" s="28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H94" s="28">
         <v>1</v>
@@ -5073,16 +5094,16 @@
         <v>37</v>
       </c>
       <c r="B95" s="21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C95" s="21" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D95" s="21" t="s">
-        <v>65</v>
+        <v>224</v>
       </c>
       <c r="E95" s="28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F95" s="28">
         <v>1</v>
@@ -5099,76 +5120,76 @@
         <v>37</v>
       </c>
       <c r="B96" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C96" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="D96" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="E96" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="F96" s="28">
+        <v>1</v>
+      </c>
+      <c r="G96" s="28">
+        <v>0</v>
+      </c>
+      <c r="H96" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B97" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="C97" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="D97" s="22" t="s">
+        <v>226</v>
+      </c>
+      <c r="E97" s="29" t="s">
+        <v>172</v>
+      </c>
+      <c r="F97" s="29">
+        <v>1</v>
+      </c>
+      <c r="G97" s="29">
+        <v>0</v>
+      </c>
+      <c r="H97" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B98" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C96" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="D96" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="E96" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="F96" s="28">
-        <v>1</v>
-      </c>
-      <c r="G96" s="28">
-        <v>0</v>
-      </c>
-      <c r="H96" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B97" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C97" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="D97" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="E97" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="F97" s="28">
-        <v>1</v>
-      </c>
-      <c r="G97" s="28">
-        <v>0</v>
-      </c>
-      <c r="H97" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="B98" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C98" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="D98" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="E98" s="29" t="s">
-        <v>173</v>
-      </c>
-      <c r="F98" s="29">
-        <v>1</v>
-      </c>
-      <c r="G98" s="29">
-        <v>1</v>
-      </c>
-      <c r="H98" s="29">
+      <c r="C98" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="D98" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="E98" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="F98" s="28">
+        <v>1</v>
+      </c>
+      <c r="G98" s="28">
+        <v>1</v>
+      </c>
+      <c r="H98" s="28">
         <v>1</v>
       </c>
     </row>
@@ -5177,16 +5198,16 @@
         <v>37</v>
       </c>
       <c r="B99" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C99" s="21" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D99" s="21" t="s">
-        <v>243</v>
+        <v>65</v>
       </c>
       <c r="E99" s="28" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="F99" s="28">
         <v>1</v>
@@ -5203,16 +5224,16 @@
         <v>37</v>
       </c>
       <c r="B100" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C100" s="21" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D100" s="21" t="s">
-        <v>244</v>
+        <v>66</v>
       </c>
       <c r="E100" s="28" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="F100" s="28">
         <v>1</v>
@@ -5229,76 +5250,76 @@
         <v>37</v>
       </c>
       <c r="B101" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="C101" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="D101" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="E101" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="F101" s="28">
+        <v>1</v>
+      </c>
+      <c r="G101" s="28">
+        <v>0</v>
+      </c>
+      <c r="H101" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B102" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C102" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="D102" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="E102" s="29" t="s">
+        <v>172</v>
+      </c>
+      <c r="F102" s="29">
+        <v>1</v>
+      </c>
+      <c r="G102" s="29">
+        <v>1</v>
+      </c>
+      <c r="H102" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B103" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C101" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="D101" s="21" t="s">
-        <v>245</v>
-      </c>
-      <c r="E101" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="F101" s="28">
-        <v>1</v>
-      </c>
-      <c r="G101" s="28">
-        <v>0</v>
-      </c>
-      <c r="H101" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B102" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="C102" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="D102" s="21" t="s">
-        <v>246</v>
-      </c>
-      <c r="E102" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="F102" s="28">
-        <v>1</v>
-      </c>
-      <c r="G102" s="28">
-        <v>0</v>
-      </c>
-      <c r="H102" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="B103" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="C103" s="22" t="s">
-        <v>145</v>
-      </c>
-      <c r="D103" s="22" t="s">
-        <v>247</v>
-      </c>
-      <c r="E103" s="29" t="s">
-        <v>167</v>
-      </c>
-      <c r="F103" s="29">
-        <v>1</v>
-      </c>
-      <c r="G103" s="29">
-        <v>0</v>
-      </c>
-      <c r="H103" s="29">
+      <c r="C103" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="D103" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="E103" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="F103" s="28">
+        <v>1</v>
+      </c>
+      <c r="G103" s="28">
+        <v>0</v>
+      </c>
+      <c r="H103" s="28">
         <v>1</v>
       </c>
     </row>
@@ -5307,16 +5328,16 @@
         <v>37</v>
       </c>
       <c r="B104" s="21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C104" s="21" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D104" s="21" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="E104" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F104" s="28">
         <v>1</v>
@@ -5333,16 +5354,16 @@
         <v>37</v>
       </c>
       <c r="B105" s="21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C105" s="21" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D105" s="21" t="s">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="E105" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F105" s="28">
         <v>1</v>
@@ -5359,76 +5380,76 @@
         <v>37</v>
       </c>
       <c r="B106" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C106" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="D106" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="E106" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="F106" s="28">
+        <v>1</v>
+      </c>
+      <c r="G106" s="28">
+        <v>0</v>
+      </c>
+      <c r="H106" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B107" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C107" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="D107" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="E107" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="F107" s="29">
+        <v>1</v>
+      </c>
+      <c r="G107" s="29">
+        <v>0</v>
+      </c>
+      <c r="H107" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B108" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C106" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="D106" s="21" t="s">
-        <v>250</v>
-      </c>
-      <c r="E106" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="F106" s="28">
-        <v>1</v>
-      </c>
-      <c r="G106" s="28">
-        <v>0</v>
-      </c>
-      <c r="H106" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B107" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="C107" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="D107" s="21" t="s">
-        <v>251</v>
-      </c>
-      <c r="E107" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="F107" s="28">
-        <v>1</v>
-      </c>
-      <c r="G107" s="28">
-        <v>0</v>
-      </c>
-      <c r="H107" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="B108" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="C108" s="22" t="s">
-        <v>146</v>
-      </c>
-      <c r="D108" s="22" t="s">
-        <v>252</v>
-      </c>
-      <c r="E108" s="29" t="s">
-        <v>167</v>
-      </c>
-      <c r="F108" s="29">
-        <v>1</v>
-      </c>
-      <c r="G108" s="29">
-        <v>0</v>
-      </c>
-      <c r="H108" s="29">
+      <c r="C108" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="D108" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="E108" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="F108" s="28">
+        <v>1</v>
+      </c>
+      <c r="G108" s="28">
+        <v>0</v>
+      </c>
+      <c r="H108" s="28">
         <v>1</v>
       </c>
     </row>
@@ -5437,22 +5458,22 @@
         <v>37</v>
       </c>
       <c r="B109" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C109" s="21" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D109" s="21" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="E109" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F109" s="28">
         <v>1</v>
       </c>
       <c r="G109" s="28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H109" s="28">
         <v>1</v>
@@ -5463,22 +5484,22 @@
         <v>37</v>
       </c>
       <c r="B110" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C110" s="21" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D110" s="21" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="E110" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F110" s="28">
         <v>1</v>
       </c>
       <c r="G110" s="28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H110" s="28">
         <v>1</v>
@@ -5489,22 +5510,22 @@
         <v>37</v>
       </c>
       <c r="B111" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C111" s="21" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D111" s="21" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="E111" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F111" s="28">
         <v>1</v>
       </c>
       <c r="G111" s="28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H111" s="28">
         <v>1</v>
@@ -5515,50 +5536,50 @@
         <v>37</v>
       </c>
       <c r="B112" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C112" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="D112" s="22" t="s">
+        <v>236</v>
+      </c>
+      <c r="E112" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="F112" s="29">
+        <v>1</v>
+      </c>
+      <c r="G112" s="29">
+        <v>0</v>
+      </c>
+      <c r="H112" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B113" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C112" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="D112" s="22" t="s">
-        <v>256</v>
-      </c>
-      <c r="E112" s="29" t="s">
-        <v>167</v>
-      </c>
-      <c r="F112" s="29">
-        <v>1</v>
-      </c>
-      <c r="G112" s="29">
-        <v>1</v>
-      </c>
-      <c r="H112" s="29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A113" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="B113" s="23" t="s">
-        <v>294</v>
-      </c>
       <c r="C113" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="D113" s="23" t="s">
-        <v>295</v>
-      </c>
-      <c r="E113" s="30" t="s">
-        <v>163</v>
-      </c>
-      <c r="F113" s="30">
-        <v>0</v>
-      </c>
-      <c r="G113" s="30">
-        <v>0</v>
-      </c>
-      <c r="H113" s="30">
+        <v>146</v>
+      </c>
+      <c r="D113" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="E113" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="F113" s="28">
+        <v>1</v>
+      </c>
+      <c r="G113" s="28">
+        <v>1</v>
+      </c>
+      <c r="H113" s="28">
         <v>1</v>
       </c>
     </row>
@@ -5567,22 +5588,22 @@
         <v>37</v>
       </c>
       <c r="B114" s="21" t="s">
-        <v>294</v>
+        <v>25</v>
       </c>
       <c r="C114" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="D114" s="25" t="s">
-        <v>296</v>
+        <v>146</v>
+      </c>
+      <c r="D114" s="21" t="s">
+        <v>238</v>
       </c>
       <c r="E114" s="28" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F114" s="28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G114" s="28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H114" s="28">
         <v>1</v>
@@ -5593,76 +5614,76 @@
         <v>37</v>
       </c>
       <c r="B115" s="21" t="s">
-        <v>294</v>
+        <v>25</v>
       </c>
       <c r="C115" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="D115" s="25" t="s">
-        <v>297</v>
+        <v>146</v>
+      </c>
+      <c r="D115" s="21" t="s">
+        <v>239</v>
       </c>
       <c r="E115" s="28" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F115" s="28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G115" s="28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H115" s="28">
         <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A116" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B116" s="21" t="s">
-        <v>294</v>
-      </c>
-      <c r="C116" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="D116" s="25" t="s">
-        <v>298</v>
-      </c>
-      <c r="E116" s="28" t="s">
-        <v>163</v>
-      </c>
-      <c r="F116" s="28">
-        <v>0</v>
-      </c>
-      <c r="G116" s="28">
-        <v>0</v>
-      </c>
-      <c r="H116" s="28">
+      <c r="A116" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B116" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="C116" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="D116" s="22" t="s">
+        <v>240</v>
+      </c>
+      <c r="E116" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="F116" s="29">
+        <v>1</v>
+      </c>
+      <c r="G116" s="29">
+        <v>1</v>
+      </c>
+      <c r="H116" s="29">
         <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A117" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B117" s="21" t="s">
-        <v>294</v>
+      <c r="A117" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="B117" s="23" t="s">
+        <v>273</v>
       </c>
       <c r="C117" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="D117" s="25" t="s">
-        <v>299</v>
-      </c>
-      <c r="E117" s="28" t="s">
-        <v>163</v>
-      </c>
-      <c r="F117" s="28">
-        <v>0</v>
-      </c>
-      <c r="G117" s="28">
-        <v>0</v>
-      </c>
-      <c r="H117" s="28">
+        <v>154</v>
+      </c>
+      <c r="D117" s="23" t="s">
+        <v>274</v>
+      </c>
+      <c r="E117" s="30" t="s">
+        <v>162</v>
+      </c>
+      <c r="F117" s="30">
+        <v>0</v>
+      </c>
+      <c r="G117" s="30">
+        <v>0</v>
+      </c>
+      <c r="H117" s="30">
         <v>1</v>
       </c>
     </row>
@@ -5671,16 +5692,16 @@
         <v>37</v>
       </c>
       <c r="B118" s="21" t="s">
-        <v>294</v>
+        <v>273</v>
       </c>
       <c r="C118" s="21" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D118" s="25" t="s">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="E118" s="28" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F118" s="28">
         <v>0</v>
@@ -5693,28 +5714,28 @@
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A119" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="B119" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="C119" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="D119" s="23" t="s">
-        <v>301</v>
-      </c>
-      <c r="E119" s="30" t="s">
-        <v>163</v>
-      </c>
-      <c r="F119" s="30">
-        <v>0</v>
-      </c>
-      <c r="G119" s="30">
-        <v>0</v>
-      </c>
-      <c r="H119" s="30">
+      <c r="A119" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B119" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="C119" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="D119" s="25" t="s">
+        <v>276</v>
+      </c>
+      <c r="E119" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="F119" s="28">
+        <v>0</v>
+      </c>
+      <c r="G119" s="28">
+        <v>0</v>
+      </c>
+      <c r="H119" s="28">
         <v>1</v>
       </c>
     </row>
@@ -5723,16 +5744,16 @@
         <v>37</v>
       </c>
       <c r="B120" s="21" t="s">
-        <v>26</v>
+        <v>273</v>
       </c>
       <c r="C120" s="21" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D120" s="25" t="s">
-        <v>302</v>
+        <v>277</v>
       </c>
       <c r="E120" s="28" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F120" s="28">
         <v>0</v>
@@ -5749,16 +5770,16 @@
         <v>37</v>
       </c>
       <c r="B121" s="21" t="s">
-        <v>26</v>
+        <v>273</v>
       </c>
       <c r="C121" s="21" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D121" s="25" t="s">
-        <v>303</v>
+        <v>278</v>
       </c>
       <c r="E121" s="28" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F121" s="28">
         <v>0</v>
@@ -5775,102 +5796,102 @@
         <v>37</v>
       </c>
       <c r="B122" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="C122" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="D122" s="25" t="s">
+        <v>279</v>
+      </c>
+      <c r="E122" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="F122" s="28">
+        <v>0</v>
+      </c>
+      <c r="G122" s="28">
+        <v>0</v>
+      </c>
+      <c r="H122" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="B123" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="C122" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="D122" s="25" t="s">
-        <v>304</v>
-      </c>
-      <c r="E122" s="28" t="s">
-        <v>163</v>
-      </c>
-      <c r="F122" s="28">
-        <v>0</v>
-      </c>
-      <c r="G122" s="28">
-        <v>0</v>
-      </c>
-      <c r="H122" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A123" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B123" s="21" t="s">
+      <c r="C123" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="D123" s="23" t="s">
+        <v>280</v>
+      </c>
+      <c r="E123" s="30" t="s">
+        <v>162</v>
+      </c>
+      <c r="F123" s="30">
+        <v>0</v>
+      </c>
+      <c r="G123" s="30">
+        <v>0</v>
+      </c>
+      <c r="H123" s="30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B124" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C123" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="D123" s="25" t="s">
-        <v>305</v>
-      </c>
-      <c r="E123" s="28" t="s">
-        <v>163</v>
-      </c>
-      <c r="F123" s="28">
-        <v>0</v>
-      </c>
-      <c r="G123" s="28">
-        <v>0</v>
-      </c>
-      <c r="H123" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A124" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="B124" s="22" t="s">
+      <c r="C124" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="D124" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="E124" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="F124" s="28">
+        <v>0</v>
+      </c>
+      <c r="G124" s="28">
+        <v>0</v>
+      </c>
+      <c r="H124" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B125" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C124" s="22" t="s">
-        <v>156</v>
-      </c>
-      <c r="D124" s="22" t="s">
-        <v>306</v>
-      </c>
-      <c r="E124" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="F124" s="29">
-        <v>0</v>
-      </c>
-      <c r="G124" s="29">
-        <v>0</v>
-      </c>
-      <c r="H124" s="29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A125" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="B125" s="23" t="s">
-        <v>27</v>
-      </c>
       <c r="C125" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="D125" s="23" t="s">
-        <v>307</v>
-      </c>
-      <c r="E125" s="30" t="s">
-        <v>163</v>
-      </c>
-      <c r="F125" s="30">
-        <v>0</v>
-      </c>
-      <c r="G125" s="30">
-        <v>0</v>
-      </c>
-      <c r="H125" s="30">
+        <v>155</v>
+      </c>
+      <c r="D125" s="25" t="s">
+        <v>282</v>
+      </c>
+      <c r="E125" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="F125" s="28">
+        <v>0</v>
+      </c>
+      <c r="G125" s="28">
+        <v>0</v>
+      </c>
+      <c r="H125" s="28">
         <v>1</v>
       </c>
     </row>
@@ -5879,16 +5900,16 @@
         <v>37</v>
       </c>
       <c r="B126" s="21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C126" s="21" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D126" s="25" t="s">
-        <v>308</v>
+        <v>283</v>
       </c>
       <c r="E126" s="28" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F126" s="28">
         <v>0</v>
@@ -5905,128 +5926,128 @@
         <v>37</v>
       </c>
       <c r="B127" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C127" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="D127" s="25" t="s">
+        <v>284</v>
+      </c>
+      <c r="E127" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="F127" s="28">
+        <v>0</v>
+      </c>
+      <c r="G127" s="28">
+        <v>0</v>
+      </c>
+      <c r="H127" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B128" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C128" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="D128" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="E128" s="29" t="s">
+        <v>162</v>
+      </c>
+      <c r="F128" s="29">
+        <v>0</v>
+      </c>
+      <c r="G128" s="29">
+        <v>0</v>
+      </c>
+      <c r="H128" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="B129" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="C127" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="D127" s="25" t="s">
-        <v>309</v>
-      </c>
-      <c r="E127" s="28" t="s">
-        <v>163</v>
-      </c>
-      <c r="F127" s="28">
-        <v>0</v>
-      </c>
-      <c r="G127" s="28">
-        <v>0</v>
-      </c>
-      <c r="H127" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A128" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B128" s="21" t="s">
+      <c r="C129" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="D129" s="23" t="s">
+        <v>286</v>
+      </c>
+      <c r="E129" s="30" t="s">
+        <v>162</v>
+      </c>
+      <c r="F129" s="30">
+        <v>0</v>
+      </c>
+      <c r="G129" s="30">
+        <v>0</v>
+      </c>
+      <c r="H129" s="30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B130" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C128" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="D128" s="25" t="s">
-        <v>310</v>
-      </c>
-      <c r="E128" s="28" t="s">
-        <v>163</v>
-      </c>
-      <c r="F128" s="28">
-        <v>0</v>
-      </c>
-      <c r="G128" s="28">
-        <v>0</v>
-      </c>
-      <c r="H128" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A129" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B129" s="21" t="s">
+      <c r="C130" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="D130" s="25" t="s">
+        <v>287</v>
+      </c>
+      <c r="E130" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="F130" s="28">
+        <v>0</v>
+      </c>
+      <c r="G130" s="28">
+        <v>0</v>
+      </c>
+      <c r="H130" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B131" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C129" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="D129" s="25" t="s">
-        <v>311</v>
-      </c>
-      <c r="E129" s="28" t="s">
-        <v>163</v>
-      </c>
-      <c r="F129" s="28">
-        <v>0</v>
-      </c>
-      <c r="G129" s="28">
-        <v>0</v>
-      </c>
-      <c r="H129" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A130" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="B130" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="C130" s="22" t="s">
-        <v>157</v>
-      </c>
-      <c r="D130" s="22" t="s">
-        <v>312</v>
-      </c>
-      <c r="E130" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="F130" s="29">
-        <v>0</v>
-      </c>
-      <c r="G130" s="29">
-        <v>0</v>
-      </c>
-      <c r="H130" s="29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A131" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="B131" s="23" t="s">
-        <v>28</v>
-      </c>
       <c r="C131" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="D131" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="E131" s="30" t="s">
-        <v>163</v>
-      </c>
-      <c r="F131" s="30">
-        <v>0</v>
-      </c>
-      <c r="G131" s="30">
-        <v>0</v>
-      </c>
-      <c r="H131" s="30">
+        <v>156</v>
+      </c>
+      <c r="D131" s="25" t="s">
+        <v>288</v>
+      </c>
+      <c r="E131" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="F131" s="28">
+        <v>0</v>
+      </c>
+      <c r="G131" s="28">
+        <v>0</v>
+      </c>
+      <c r="H131" s="28">
         <v>1</v>
       </c>
     </row>
@@ -6035,16 +6056,16 @@
         <v>37</v>
       </c>
       <c r="B132" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C132" s="21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D132" s="25" t="s">
-        <v>69</v>
+        <v>289</v>
       </c>
       <c r="E132" s="28" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F132" s="28">
         <v>0</v>
@@ -6061,102 +6082,102 @@
         <v>37</v>
       </c>
       <c r="B133" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C133" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="D133" s="25" t="s">
+        <v>290</v>
+      </c>
+      <c r="E133" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="F133" s="28">
+        <v>0</v>
+      </c>
+      <c r="G133" s="28">
+        <v>0</v>
+      </c>
+      <c r="H133" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B134" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C134" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="D134" s="22" t="s">
+        <v>291</v>
+      </c>
+      <c r="E134" s="29" t="s">
+        <v>162</v>
+      </c>
+      <c r="F134" s="29">
+        <v>0</v>
+      </c>
+      <c r="G134" s="29">
+        <v>0</v>
+      </c>
+      <c r="H134" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="B135" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="C133" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="D133" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="E133" s="28" t="s">
-        <v>163</v>
-      </c>
-      <c r="F133" s="28">
-        <v>0</v>
-      </c>
-      <c r="G133" s="28">
-        <v>0</v>
-      </c>
-      <c r="H133" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A134" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B134" s="21" t="s">
+      <c r="C135" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="D135" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="E135" s="30" t="s">
+        <v>162</v>
+      </c>
+      <c r="F135" s="30">
+        <v>0</v>
+      </c>
+      <c r="G135" s="30">
+        <v>0</v>
+      </c>
+      <c r="H135" s="30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B136" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="C134" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="D134" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="E134" s="28" t="s">
-        <v>163</v>
-      </c>
-      <c r="F134" s="28">
-        <v>0</v>
-      </c>
-      <c r="G134" s="28">
-        <v>0</v>
-      </c>
-      <c r="H134" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A135" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B135" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="C135" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="D135" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="E135" s="28" t="s">
-        <v>163</v>
-      </c>
-      <c r="F135" s="28">
-        <v>0</v>
-      </c>
-      <c r="G135" s="28">
-        <v>0</v>
-      </c>
-      <c r="H135" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A136" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="B136" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="C136" s="22" t="s">
-        <v>158</v>
-      </c>
-      <c r="D136" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="E136" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="F136" s="29">
-        <v>0</v>
-      </c>
-      <c r="G136" s="29">
-        <v>0</v>
-      </c>
-      <c r="H136" s="29">
+      <c r="C136" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="D136" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="E136" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="F136" s="28">
+        <v>0</v>
+      </c>
+      <c r="G136" s="28">
+        <v>0</v>
+      </c>
+      <c r="H136" s="28">
         <v>1</v>
       </c>
     </row>
@@ -6165,25 +6186,25 @@
         <v>37</v>
       </c>
       <c r="B137" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="C137" s="25" t="s">
-        <v>189</v>
-      </c>
-      <c r="D137" s="49" t="s">
-        <v>278</v>
+        <v>28</v>
+      </c>
+      <c r="C137" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="D137" s="25" t="s">
+        <v>70</v>
       </c>
       <c r="E137" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="F137" s="45">
-        <v>0</v>
-      </c>
-      <c r="G137" s="45">
-        <v>0</v>
-      </c>
-      <c r="H137" s="45">
-        <v>0</v>
+        <v>162</v>
+      </c>
+      <c r="F137" s="28">
+        <v>0</v>
+      </c>
+      <c r="G137" s="28">
+        <v>0</v>
+      </c>
+      <c r="H137" s="28">
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
@@ -6191,25 +6212,25 @@
         <v>37</v>
       </c>
       <c r="B138" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="C138" s="25" t="s">
-        <v>189</v>
-      </c>
-      <c r="D138" s="21" t="s">
-        <v>279</v>
+        <v>28</v>
+      </c>
+      <c r="C138" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="D138" s="25" t="s">
+        <v>71</v>
       </c>
       <c r="E138" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="F138" s="45">
-        <v>0</v>
-      </c>
-      <c r="G138" s="45">
-        <v>0</v>
-      </c>
-      <c r="H138" s="45">
-        <v>0</v>
+        <v>162</v>
+      </c>
+      <c r="F138" s="28">
+        <v>0</v>
+      </c>
+      <c r="G138" s="28">
+        <v>0</v>
+      </c>
+      <c r="H138" s="28">
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
@@ -6217,77 +6238,77 @@
         <v>37</v>
       </c>
       <c r="B139" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="C139" s="25" t="s">
-        <v>189</v>
-      </c>
-      <c r="D139" s="21" t="s">
-        <v>280</v>
+        <v>28</v>
+      </c>
+      <c r="C139" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="D139" s="25" t="s">
+        <v>72</v>
       </c>
       <c r="E139" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="F139" s="45">
-        <v>0</v>
-      </c>
-      <c r="G139" s="45">
-        <v>0</v>
-      </c>
-      <c r="H139" s="45">
-        <v>0</v>
+        <v>162</v>
+      </c>
+      <c r="F139" s="28">
+        <v>0</v>
+      </c>
+      <c r="G139" s="28">
+        <v>0</v>
+      </c>
+      <c r="H139" s="28">
+        <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A140" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B140" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="C140" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="D140" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="E140" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="F140" s="45">
-        <v>0</v>
-      </c>
-      <c r="G140" s="45">
-        <v>0</v>
-      </c>
-      <c r="H140" s="45">
-        <v>0</v>
+      <c r="A140" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B140" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C140" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="D140" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E140" s="29" t="s">
+        <v>162</v>
+      </c>
+      <c r="F140" s="29">
+        <v>0</v>
+      </c>
+      <c r="G140" s="29">
+        <v>0</v>
+      </c>
+      <c r="H140" s="29">
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A141" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="B141" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="C141" s="22" t="s">
-        <v>189</v>
-      </c>
-      <c r="D141" s="50" t="s">
-        <v>282</v>
-      </c>
-      <c r="E141" s="29" t="s">
-        <v>167</v>
-      </c>
-      <c r="F141" s="46">
-        <v>0</v>
-      </c>
-      <c r="G141" s="46">
-        <v>0</v>
-      </c>
-      <c r="H141" s="46">
-        <v>0</v>
+      <c r="A141" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B141" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="C141" s="25" t="s">
+        <v>188</v>
+      </c>
+      <c r="D141" s="49" t="s">
+        <v>257</v>
+      </c>
+      <c r="E141" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="F141" s="45">
+        <v>1</v>
+      </c>
+      <c r="G141" s="45">
+        <v>0</v>
+      </c>
+      <c r="H141" s="45">
+        <v>1</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -6295,23 +6316,25 @@
         <v>37</v>
       </c>
       <c r="B142" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="C142" s="25" t="s">
         <v>188</v>
       </c>
-      <c r="C142" s="25" t="s">
-        <v>182</v>
-      </c>
-      <c r="D142" s="49" t="s">
-        <v>283</v>
-      </c>
-      <c r="E142" s="45"/>
+      <c r="D142" s="21" t="s">
+        <v>258</v>
+      </c>
+      <c r="E142" s="28" t="s">
+        <v>166</v>
+      </c>
       <c r="F142" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G142" s="45">
         <v>0</v>
       </c>
       <c r="H142" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -6319,23 +6342,25 @@
         <v>37</v>
       </c>
       <c r="B143" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="C143" s="25" t="s">
         <v>188</v>
       </c>
-      <c r="C143" s="25" t="s">
-        <v>182</v>
-      </c>
       <c r="D143" s="21" t="s">
-        <v>284</v>
-      </c>
-      <c r="E143" s="45"/>
+        <v>259</v>
+      </c>
+      <c r="E143" s="28" t="s">
+        <v>166</v>
+      </c>
       <c r="F143" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G143" s="45">
         <v>0</v>
       </c>
       <c r="H143" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -6343,71 +6368,77 @@
         <v>37</v>
       </c>
       <c r="B144" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="C144" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="C144" s="25" t="s">
-        <v>182</v>
-      </c>
       <c r="D144" s="21" t="s">
-        <v>285</v>
-      </c>
-      <c r="E144" s="45"/>
+        <v>260</v>
+      </c>
+      <c r="E144" s="28" t="s">
+        <v>166</v>
+      </c>
       <c r="F144" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G144" s="45">
         <v>0</v>
       </c>
       <c r="H144" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A145" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B145" s="21" t="s">
+      <c r="A145" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B145" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="C145" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="C145" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="D145" s="21" t="s">
-        <v>286</v>
-      </c>
-      <c r="E145" s="45"/>
-      <c r="F145" s="45">
-        <v>0</v>
-      </c>
-      <c r="G145" s="45">
-        <v>0</v>
-      </c>
-      <c r="H145" s="45">
-        <v>0</v>
+      <c r="D145" s="50" t="s">
+        <v>261</v>
+      </c>
+      <c r="E145" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="F145" s="46">
+        <v>1</v>
+      </c>
+      <c r="G145" s="46">
+        <v>0</v>
+      </c>
+      <c r="H145" s="46">
+        <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A146" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="B146" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="C146" s="22" t="s">
-        <v>182</v>
-      </c>
-      <c r="D146" s="50" t="s">
-        <v>287</v>
-      </c>
-      <c r="E146" s="46"/>
-      <c r="F146" s="46">
-        <v>0</v>
-      </c>
-      <c r="G146" s="46">
-        <v>0</v>
-      </c>
-      <c r="H146" s="46">
-        <v>0</v>
+      <c r="A146" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B146" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="C146" s="25" t="s">
+        <v>308</v>
+      </c>
+      <c r="D146" s="49" t="s">
+        <v>262</v>
+      </c>
+      <c r="E146" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="F146" s="45">
+        <v>1</v>
+      </c>
+      <c r="G146" s="45">
+        <v>0</v>
+      </c>
+      <c r="H146" s="45">
+        <v>1</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
@@ -6418,20 +6449,22 @@
         <v>187</v>
       </c>
       <c r="C147" s="25" t="s">
-        <v>183</v>
-      </c>
-      <c r="D147" s="49" t="s">
-        <v>288</v>
-      </c>
-      <c r="E147" s="45"/>
+        <v>308</v>
+      </c>
+      <c r="D147" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="E147" s="45" t="s">
+        <v>160</v>
+      </c>
       <c r="F147" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G147" s="45">
         <v>0</v>
       </c>
       <c r="H147" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
@@ -6442,20 +6475,22 @@
         <v>187</v>
       </c>
       <c r="C148" s="25" t="s">
-        <v>183</v>
+        <v>308</v>
       </c>
       <c r="D148" s="21" t="s">
-        <v>289</v>
-      </c>
-      <c r="E148" s="45"/>
+        <v>264</v>
+      </c>
+      <c r="E148" s="45" t="s">
+        <v>160</v>
+      </c>
       <c r="F148" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G148" s="45">
         <v>0</v>
       </c>
       <c r="H148" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -6465,69 +6500,75 @@
       <c r="B149" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="C149" s="25" t="s">
-        <v>183</v>
+      <c r="C149" s="21" t="s">
+        <v>308</v>
       </c>
       <c r="D149" s="21" t="s">
-        <v>290</v>
-      </c>
-      <c r="E149" s="45"/>
+        <v>265</v>
+      </c>
+      <c r="E149" s="45" t="s">
+        <v>160</v>
+      </c>
       <c r="F149" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G149" s="45">
         <v>0</v>
       </c>
       <c r="H149" s="45">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A150" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B150" s="21" t="s">
+      <c r="A150" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B150" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="C150" s="21" t="s">
-        <v>183</v>
-      </c>
-      <c r="D150" s="21" t="s">
-        <v>291</v>
-      </c>
-      <c r="E150" s="45"/>
-      <c r="F150" s="45">
-        <v>0</v>
-      </c>
-      <c r="G150" s="45">
-        <v>0</v>
-      </c>
-      <c r="H150" s="45">
-        <v>0</v>
+      <c r="C150" s="22" t="s">
+        <v>308</v>
+      </c>
+      <c r="D150" s="50" t="s">
+        <v>266</v>
+      </c>
+      <c r="E150" s="46" t="s">
+        <v>160</v>
+      </c>
+      <c r="F150" s="46">
+        <v>1</v>
+      </c>
+      <c r="G150" s="46">
+        <v>0</v>
+      </c>
+      <c r="H150" s="46">
+        <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A151" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="B151" s="22" t="s">
-        <v>187</v>
-      </c>
-      <c r="C151" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="D151" s="50" t="s">
-        <v>292</v>
-      </c>
-      <c r="E151" s="46"/>
-      <c r="F151" s="46">
-        <v>0</v>
-      </c>
-      <c r="G151" s="46">
-        <v>0</v>
-      </c>
-      <c r="H151" s="46">
-        <v>0</v>
+      <c r="A151" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B151" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="C151" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="D151" s="49" t="s">
+        <v>267</v>
+      </c>
+      <c r="E151" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="F151" s="45">
+        <v>1</v>
+      </c>
+      <c r="G151" s="45">
+        <v>0</v>
+      </c>
+      <c r="H151" s="45">
+        <v>1</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
@@ -6535,25 +6576,25 @@
         <v>37</v>
       </c>
       <c r="B152" s="21" t="s">
-        <v>29</v>
+        <v>186</v>
       </c>
       <c r="C152" s="25" t="s">
-        <v>148</v>
+        <v>182</v>
       </c>
       <c r="D152" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="E152" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="F152" s="28">
-        <v>0</v>
-      </c>
-      <c r="G152" s="28">
-        <v>0</v>
-      </c>
-      <c r="H152" s="28">
-        <v>0</v>
+        <v>268</v>
+      </c>
+      <c r="E152" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="F152" s="45">
+        <v>1</v>
+      </c>
+      <c r="G152" s="45">
+        <v>0</v>
+      </c>
+      <c r="H152" s="45">
+        <v>1</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
@@ -6561,77 +6602,77 @@
         <v>37</v>
       </c>
       <c r="B153" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C153" s="21" t="s">
-        <v>148</v>
+        <v>186</v>
+      </c>
+      <c r="C153" s="25" t="s">
+        <v>182</v>
       </c>
       <c r="D153" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="E153" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="F153" s="28">
-        <v>0</v>
-      </c>
-      <c r="G153" s="28">
-        <v>0</v>
-      </c>
-      <c r="H153" s="28">
-        <v>0</v>
+        <v>269</v>
+      </c>
+      <c r="E153" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="F153" s="45">
+        <v>1</v>
+      </c>
+      <c r="G153" s="45">
+        <v>0</v>
+      </c>
+      <c r="H153" s="45">
+        <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A154" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="B154" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C154" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="D154" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="E154" s="29" t="s">
-        <v>161</v>
-      </c>
-      <c r="F154" s="29">
-        <v>0</v>
-      </c>
-      <c r="G154" s="29">
-        <v>0</v>
-      </c>
-      <c r="H154" s="29">
-        <v>0</v>
+      <c r="A154" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B154" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="C154" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="D154" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="E154" s="45" t="s">
+        <v>160</v>
+      </c>
+      <c r="F154" s="45">
+        <v>1</v>
+      </c>
+      <c r="G154" s="45">
+        <v>0</v>
+      </c>
+      <c r="H154" s="45">
+        <v>1</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A155" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B155" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="C155" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="D155" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="E155" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="F155" s="28">
-        <v>0</v>
-      </c>
-      <c r="G155" s="28">
-        <v>0</v>
-      </c>
-      <c r="H155" s="28">
-        <v>0</v>
+      <c r="A155" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B155" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="C155" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="D155" s="50" t="s">
+        <v>271</v>
+      </c>
+      <c r="E155" s="46" t="s">
+        <v>160</v>
+      </c>
+      <c r="F155" s="46">
+        <v>1</v>
+      </c>
+      <c r="G155" s="46">
+        <v>0</v>
+      </c>
+      <c r="H155" s="46">
+        <v>1</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
@@ -6639,16 +6680,16 @@
         <v>37</v>
       </c>
       <c r="B156" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C156" s="25" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D156" s="21" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E156" s="28" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F156" s="28">
         <v>0</v>
@@ -6661,55 +6702,55 @@
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A157" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="B157" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="C157" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="D157" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="E157" s="29" t="s">
-        <v>161</v>
-      </c>
-      <c r="F157" s="29">
-        <v>0</v>
-      </c>
-      <c r="G157" s="29">
-        <v>0</v>
-      </c>
-      <c r="H157" s="29">
+      <c r="A157" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B157" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C157" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="D157" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="E157" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="F157" s="28">
+        <v>0</v>
+      </c>
+      <c r="G157" s="28">
+        <v>0</v>
+      </c>
+      <c r="H157" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A158" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B158" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C158" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="D158" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="E158" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F158" s="28">
-        <v>1</v>
-      </c>
-      <c r="G158" s="28">
-        <v>1</v>
-      </c>
-      <c r="H158" s="28">
-        <v>1</v>
+      <c r="A158" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B158" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C158" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="D158" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="E158" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="F158" s="29">
+        <v>0</v>
+      </c>
+      <c r="G158" s="29">
+        <v>0</v>
+      </c>
+      <c r="H158" s="29">
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -6717,25 +6758,25 @@
         <v>37</v>
       </c>
       <c r="B159" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C159" s="21" t="s">
-        <v>150</v>
+        <v>30</v>
+      </c>
+      <c r="C159" s="25" t="s">
+        <v>148</v>
       </c>
       <c r="D159" s="21" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E159" s="28" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="F159" s="28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G159" s="28">
         <v>0</v>
       </c>
       <c r="H159" s="28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -6743,82 +6784,186 @@
         <v>37</v>
       </c>
       <c r="B160" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C160" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="D160" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="E160" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="F160" s="28">
+        <v>0</v>
+      </c>
+      <c r="G160" s="28">
+        <v>0</v>
+      </c>
+      <c r="H160" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A161" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B161" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="C161" s="22" t="s">
+        <v>148</v>
+      </c>
+      <c r="D161" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="E161" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="F161" s="29">
+        <v>0</v>
+      </c>
+      <c r="G161" s="29">
+        <v>0</v>
+      </c>
+      <c r="H161" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A162" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B162" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="C160" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="D160" s="21" t="s">
+      <c r="C162" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="D162" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="E162" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="F162" s="28">
+        <v>1</v>
+      </c>
+      <c r="G162" s="28">
+        <v>1</v>
+      </c>
+      <c r="H162" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A163" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B163" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C163" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="D163" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="E163" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="F163" s="28">
+        <v>1</v>
+      </c>
+      <c r="G163" s="28">
+        <v>0</v>
+      </c>
+      <c r="H163" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A164" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B164" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C164" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="D164" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="E160" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F160" s="28">
-        <v>1</v>
-      </c>
-      <c r="G160" s="28">
-        <v>0</v>
-      </c>
-      <c r="H160" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A161" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B161" s="21" t="s">
+      <c r="E164" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="F164" s="28">
+        <v>1</v>
+      </c>
+      <c r="G164" s="28">
+        <v>0</v>
+      </c>
+      <c r="H164" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A165" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B165" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="C161" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="D161" s="21" t="s">
+      <c r="C165" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="D165" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="E161" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="F161" s="28">
-        <v>1</v>
-      </c>
-      <c r="G161" s="28">
-        <v>0</v>
-      </c>
-      <c r="H161" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="B162" s="24" t="s">
+      <c r="E165" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="F165" s="28">
+        <v>1</v>
+      </c>
+      <c r="G165" s="28">
+        <v>0</v>
+      </c>
+      <c r="H165" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" ht="14.95" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A166" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B166" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="C162" s="24" t="s">
-        <v>150</v>
-      </c>
-      <c r="D162" s="24" t="s">
+      <c r="C166" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="D166" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="E162" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="F162" s="31">
-        <v>1</v>
-      </c>
-      <c r="G162" s="31">
-        <v>1</v>
-      </c>
-      <c r="H162" s="31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="163" spans="1:8" ht="14.95" thickTop="1" x14ac:dyDescent="0.25"/>
+      <c r="E166" s="31" t="s">
+        <v>170</v>
+      </c>
+      <c r="F166" s="31">
+        <v>1</v>
+      </c>
+      <c r="G166" s="31">
+        <v>1</v>
+      </c>
+      <c r="H166" s="31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" ht="14.95" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:H162" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:H166" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
